--- a/src/main/java/video/call/data/topics.xlsx
+++ b/src/main/java/video/call/data/topics.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4332" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4231" uniqueCount="690">
   <si>
     <t>Part</t>
   </si>
@@ -1176,45 +1176,6 @@
     <t>Oh, I'm so excited. I'll go get my swimsuit now. See you later!</t>
   </si>
   <si>
-    <t>What do you have?</t>
-  </si>
-  <si>
-    <t>I have a boat.</t>
-  </si>
-  <si>
-    <t>What color is it?</t>
-  </si>
-  <si>
-    <t>My boat is blue.</t>
-  </si>
-  <si>
-    <t>Cool! Can I play with you?</t>
-  </si>
-  <si>
-    <t>Yes. We can play in the tub.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oh hey! </t>
-  </si>
-  <si>
-    <t>What's your favorite room?</t>
-  </si>
-  <si>
-    <t>It's the bathroom.</t>
-  </si>
-  <si>
-    <t>What do you do there?</t>
-  </si>
-  <si>
-    <t>I take a shower.</t>
-  </si>
-  <si>
-    <t>Is your bathroom big?</t>
-  </si>
-  <si>
-    <t>No, it's small.</t>
-  </si>
-  <si>
     <t>Hey look at the fruits in my basket. I just bought them at the market.</t>
   </si>
   <si>
@@ -1840,6 +1801,298 @@
   </si>
   <si>
     <t>We had so much fun talking about transportation. I'll see you in the next lesson. Bye bye!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi, Amy's birthday is coming soon. Let's get her some new items of clothes. </t>
+  </si>
+  <si>
+    <t>Jeans, pink dress, red dress, hat</t>
+  </si>
+  <si>
+    <t>Do you like these jeans?</t>
+  </si>
+  <si>
+    <t>Look at these jeans. Are they too big or too small for her?</t>
+  </si>
+  <si>
+    <t>They are too big for me!</t>
+  </si>
+  <si>
+    <t>User answers meaning: too big or huge</t>
+  </si>
+  <si>
+    <t>Yeah, I also think they're too big for her.</t>
+  </si>
+  <si>
+    <t>How about this dress?</t>
+  </si>
+  <si>
+    <t>User answers meaning: too small or tight or tiny</t>
+  </si>
+  <si>
+    <t>I think they're too big for her. She's small.</t>
+  </si>
+  <si>
+    <t>Wow, this dress is beautiful!</t>
+  </si>
+  <si>
+    <t>User answers meaning: Fine/ It fits her</t>
+  </si>
+  <si>
+    <t>Let's try it on!</t>
+  </si>
+  <si>
+    <t>It fits me perfectly!</t>
+  </si>
+  <si>
+    <t>Are they too big or too small for her?</t>
+  </si>
+  <si>
+    <t>Great!</t>
+  </si>
+  <si>
+    <t>User asks: Are they too big or too small for her?</t>
+  </si>
+  <si>
+    <t>I didn't catch that. Are they too big or too small for her?</t>
+  </si>
+  <si>
+    <t>So, I think they're too big for her. She's small.</t>
+  </si>
+  <si>
+    <t>So, are they too big or too small for her?</t>
+  </si>
+  <si>
+    <t>How about getting her a dress? Which one is better, purple or white?</t>
+  </si>
+  <si>
+    <t>User answers meaning: purple</t>
+  </si>
+  <si>
+    <t>Yeah, it's beautiful. Let's get her the purple dress.</t>
+  </si>
+  <si>
+    <t>User answers meaning: white</t>
+  </si>
+  <si>
+    <t>Yeah, it's beautiful. Let's get her the white dress.</t>
+  </si>
+  <si>
+    <t>User answers meaning: both purple and white</t>
+  </si>
+  <si>
+    <t>Hm...I think the purple one suits her better.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User answers meaning: a color except purple and white/ nothing
+</t>
+  </si>
+  <si>
+    <t>I think the purple one is beautiful. She likes purple.</t>
+  </si>
+  <si>
+    <t>User answers meaning: I don't know/ I'm not sure</t>
+  </si>
+  <si>
+    <t>Which dress is better, purple or white?</t>
+  </si>
+  <si>
+    <t>User asks: Which dress is better, pink or red?</t>
+  </si>
+  <si>
+    <t>Maybe the purple dress. Which one do you think is better?</t>
+  </si>
+  <si>
+    <t>I can't hear you. Which dress is better, purple or white?</t>
+  </si>
+  <si>
+    <t>I think she would like the purple dress.</t>
+  </si>
+  <si>
+    <t>Look at this hat. Do you think it fits her?</t>
+  </si>
+  <si>
+    <t>User answers meaning: Yes, it fits her./ She'll like it</t>
+  </si>
+  <si>
+    <t>Yeah. Let's buy this for her, too.</t>
+  </si>
+  <si>
+    <t>User answers meaning: No, it doesn't fit her.</t>
+  </si>
+  <si>
+    <t>Okay. I won't buy it.</t>
+  </si>
+  <si>
+    <t>Does this hat fit her?</t>
+  </si>
+  <si>
+    <t>User asks: Do you think it fits her?</t>
+  </si>
+  <si>
+    <t>Yes, I think this fits her well. Do you think so?</t>
+  </si>
+  <si>
+    <t>Huh? Do you think this hat fits her well?</t>
+  </si>
+  <si>
+    <t>I think this fits her well, so I'll buy it.</t>
+  </si>
+  <si>
+    <t>So, do you think it fits her?</t>
+  </si>
+  <si>
+    <t>Yay! We got her some very nice clothes. Let's meet each other at her birthday party next week. See you!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hello! Look at the pictures on the board! Let's play a guessing game. </t>
+  </si>
+  <si>
+    <t>board, pics of red rug, blue chair, blue lamp, plant</t>
+  </si>
+  <si>
+    <t>Is this your new rug?</t>
+  </si>
+  <si>
+    <t>Listen carefully. Question 1: Its shape is a rectangle. We put it on the floor. What is it?</t>
+  </si>
+  <si>
+    <t>Yes. This is my new rug.</t>
+  </si>
+  <si>
+    <t>User answers meaning: It's a rug.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yeah, you got it. It's a rug. </t>
+  </si>
+  <si>
+    <t>Actor points to the rug</t>
+  </si>
+  <si>
+    <t>It's nice. You have a new chair, too.</t>
+  </si>
+  <si>
+    <t>I'll give you another hint. It's red. So, what is it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes. It's a small chair. </t>
+  </si>
+  <si>
+    <t>Can I sit on it?</t>
+  </si>
+  <si>
+    <t>Sure!</t>
+  </si>
+  <si>
+    <t>I'll tell you the answer. It's a rug.</t>
+  </si>
+  <si>
+    <t>Hm...I'll give you another hint. It's red. So, what is it?</t>
+  </si>
+  <si>
+    <t>Let me help you this time. It's a rug.</t>
+  </si>
+  <si>
+    <t>Let's move to question 2: It has 4 legs. It's small. What is it?</t>
+  </si>
+  <si>
+    <t>User answers meaning: It's a chair.</t>
+  </si>
+  <si>
+    <t>Wonderful! It's a chair. We sit on it.</t>
+  </si>
+  <si>
+    <t>We can sit on it. What is it?</t>
+  </si>
+  <si>
+    <t>We can sit on it. Can you tell me what it is?</t>
+  </si>
+  <si>
+    <t>I didn't catch that. What is it?</t>
+  </si>
+  <si>
+    <t>Look! It's a chair, and it has 4 legs.</t>
+  </si>
+  <si>
+    <t>We sit on this object. So, what is it?</t>
+  </si>
+  <si>
+    <t>Oh, that isn't what I meant. The answer is: a chair!</t>
+  </si>
+  <si>
+    <t>We have 2 pictures left. So, question 3: It's small and green. What am I talking about?</t>
+  </si>
+  <si>
+    <t>User answers meaning: a plant</t>
+  </si>
+  <si>
+    <t>You're amazing! That's right. I'm talking about the plant.</t>
+  </si>
+  <si>
+    <t>You need give it water everyday. What is it?</t>
+  </si>
+  <si>
+    <t>User asks: What am I talking about?/ What is it?</t>
+  </si>
+  <si>
+    <t>It's a plant. It's green and small. Can you say "It's a plant"?</t>
+  </si>
+  <si>
+    <t>I can't hear you. It's small and green. What is it?</t>
+  </si>
+  <si>
+    <t>Don't worry if you can't get it. It's a plant.</t>
+  </si>
+  <si>
+    <t>Can you guess if I'm talking about a plant or a lamp?</t>
+  </si>
+  <si>
+    <t>Alright. What I'm talking about is a plant.</t>
+  </si>
+  <si>
+    <t>So, what do you have in your house?</t>
+  </si>
+  <si>
+    <t>Actor points to 4 pictures</t>
+  </si>
+  <si>
+    <t>User answers meaning: an item of furniture</t>
+  </si>
+  <si>
+    <t>That's very nice!</t>
+  </si>
+  <si>
+    <t>User answers meaning: plant</t>
+  </si>
+  <si>
+    <t>Nice! Don't forget to water it every day.</t>
+  </si>
+  <si>
+    <t>Sorry to hear that. But you can grow a plant. It will be fun.</t>
+  </si>
+  <si>
+    <t>Do you have a rug, a chair or a plant?</t>
+  </si>
+  <si>
+    <t>User asks the question: What do you have in your house?</t>
+  </si>
+  <si>
+    <t>I have 2 chairs and a plant in my house. What do you have?</t>
+  </si>
+  <si>
+    <t>Please say that one more time. What do you have in your house?</t>
+  </si>
+  <si>
+    <t>No worries. You can check and tell me later.</t>
+  </si>
+  <si>
+    <t>But what do you have in your house?</t>
+  </si>
+  <si>
+    <t>It's fine. You can check and tell me later.</t>
+  </si>
+  <si>
+    <t>Wonderful! We had a great time playing the guessing game today. Let's do another game soon. Bye bye!</t>
   </si>
 </sst>
 </file>
@@ -3234,7 +3487,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3274,7 +3527,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>501</v>
+        <v>593</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -3283,13 +3536,13 @@
         <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>502</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>7</v>
+        <v>594</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>503</v>
+        <v>595</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -3303,7 +3556,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>504</v>
+        <v>596</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -3315,10 +3568,10 @@
         <v>7</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>505</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>506</v>
+        <v>597</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -3329,10 +3582,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>507</v>
+        <v>598</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>508</v>
+        <v>599</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -3347,7 +3600,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>509</v>
+        <v>600</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -3358,10 +3611,10 @@
         <v>24</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>510</v>
+        <v>601</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>511</v>
+        <v>602</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>27</v>
@@ -3376,7 +3629,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>512</v>
+        <v>603</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -3384,19 +3637,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>71</v>
+        <v>604</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>513</v>
+        <v>602</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>7</v>
@@ -3405,7 +3658,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>514</v>
+        <v>605</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -3413,19 +3666,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>515</v>
+        <v>218</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>516</v>
+        <v>602</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>7</v>
@@ -3434,7 +3687,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>517</v>
+        <v>606</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -3442,16 +3695,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>518</v>
+        <v>607</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>7</v>
@@ -3461,6 +3714,9 @@
       </c>
       <c r="G8" t="s" s="0">
         <v>7</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>608</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>7</v>
@@ -3468,16 +3724,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>40</v>
+        <v>609</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>519</v>
+        <v>602</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>7</v>
@@ -3486,9 +3742,6 @@
         <v>7</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H9" t="s" s="0">
         <v>7</v>
       </c>
       <c r="I9" t="s" s="0">
@@ -3497,16 +3750,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>520</v>
+        <v>610</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>7</v>
@@ -3515,9 +3768,6 @@
         <v>7</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H10" t="s" s="0">
         <v>7</v>
       </c>
       <c r="I10" t="s" s="0">
@@ -3526,16 +3776,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>521</v>
+        <v>611</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>7</v>
@@ -3555,16 +3805,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>168</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>7</v>
+        <v>612</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -3584,16 +3834,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>522</v>
+        <v>602</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>7</v>
@@ -3613,19 +3863,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>523</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>524</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s" s="0">
         <v>7</v>
@@ -3642,19 +3892,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>62</v>
+        <v>465</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>525</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>526</v>
+        <v>613</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s" s="0">
         <v>7</v>
@@ -3671,19 +3921,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>25</v>
+        <v>614</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>527</v>
+        <v>615</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s" s="0">
         <v>7</v>
@@ -3700,19 +3950,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>528</v>
+        <v>616</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>529</v>
+        <v>617</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s" s="0">
         <v>7</v>
@@ -3729,19 +3979,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>35</v>
+        <v>618</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>530</v>
+        <v>619</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s" s="0">
         <v>7</v>
@@ -3758,19 +4008,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>40</v>
+        <v>620</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>531</v>
+        <v>621</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s" s="0">
         <v>7</v>
@@ -3787,16 +4037,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>45</v>
+        <v>622</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>532</v>
+        <v>619</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>7</v>
@@ -3816,16 +4066,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>533</v>
+        <v>623</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>7</v>
@@ -3845,16 +4095,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>53</v>
+        <v>624</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>7</v>
+        <v>625</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>7</v>
@@ -3874,16 +4124,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>534</v>
+        <v>626</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>7</v>
@@ -3903,19 +4153,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>535</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>536</v>
+        <v>627</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s" s="0">
         <v>7</v>
@@ -3932,19 +4182,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>537</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>538</v>
+        <v>623</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s" s="0">
         <v>7</v>
@@ -3961,19 +4211,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>303</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>539</v>
+        <v>627</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s" s="0">
         <v>7</v>
@@ -3990,16 +4240,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>540</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>7</v>
@@ -4019,16 +4269,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>541</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>542</v>
+        <v>628</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>7</v>
@@ -4048,19 +4298,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>35</v>
+        <v>629</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>543</v>
+        <v>630</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E29" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F29" t="s" s="0">
         <v>7</v>
@@ -4077,19 +4327,19 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>40</v>
+        <v>631</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>544</v>
+        <v>632</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F30" t="s" s="0">
         <v>7</v>
@@ -4106,16 +4356,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>540</v>
+        <v>633</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>7</v>
@@ -4135,16 +4385,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>195</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>49</v>
+        <v>634</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>545</v>
+        <v>635</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>253</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>7</v>
@@ -4164,16 +4414,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>254</v>
+        <v>111</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>7</v>
+        <v>636</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>255</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>7</v>
@@ -4193,16 +4443,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>546</v>
+        <v>637</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>7</v>
@@ -4222,19 +4472,19 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>301</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>547</v>
+        <v>638</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s" s="0">
         <v>7</v>
@@ -4251,16 +4501,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>548</v>
+        <v>637</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -4280,16 +4530,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>306</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>549</v>
+        <v>7</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -4309,16 +4559,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>550</v>
+        <v>639</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -4333,151 +4583,6 @@
         <v>7</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="0">
-        <v>140</v>
-      </c>
-      <c r="B39" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="C39" t="s" s="0">
-        <v>309</v>
-      </c>
-      <c r="D39" t="s" s="0">
-        <v>142</v>
-      </c>
-      <c r="E39" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G39" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H39" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I39" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="0">
-        <v>143</v>
-      </c>
-      <c r="B40" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="C40" t="s" s="0">
-        <v>551</v>
-      </c>
-      <c r="D40" t="s" s="0">
-        <v>145</v>
-      </c>
-      <c r="E40" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G40" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H40" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I40" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="C41" t="s" s="0">
-        <v>311</v>
-      </c>
-      <c r="D41" t="s" s="0">
-        <v>148</v>
-      </c>
-      <c r="E41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I41" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="0">
-        <v>149</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D42" t="s" s="0">
-        <v>151</v>
-      </c>
-      <c r="E42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I42" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="0">
-        <v>154</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>552</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>156</v>
-      </c>
-      <c r="E43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I43" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -4488,7 +4593,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4528,7 +4633,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>553</v>
+        <v>640</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -4540,10 +4645,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>554</v>
+        <v>641</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>555</v>
+        <v>642</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -4557,7 +4662,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>556</v>
+        <v>643</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -4572,7 +4677,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>557</v>
+        <v>644</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -4583,10 +4688,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>558</v>
+        <v>645</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>559</v>
+        <v>646</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -4595,13 +4700,13 @@
         <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>7</v>
+        <v>647</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>560</v>
+        <v>648</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -4615,7 +4720,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>561</v>
+        <v>649</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>27</v>
@@ -4630,7 +4735,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>562</v>
+        <v>650</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -4641,10 +4746,10 @@
         <v>29</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>563</v>
+        <v>649</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>32</v>
@@ -4659,7 +4764,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>564</v>
+        <v>651</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -4673,7 +4778,7 @@
         <v>35</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>37</v>
@@ -4688,7 +4793,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>565</v>
+        <v>652</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -4702,7 +4807,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>566</v>
+        <v>653</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>42</v>
@@ -4711,7 +4816,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>7</v>
+        <v>647</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>7</v>
@@ -4731,7 +4836,7 @@
         <v>45</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>567</v>
+        <v>654</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>47</v>
@@ -4760,7 +4865,7 @@
         <v>49</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>568</v>
+        <v>655</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>51</v>
@@ -4769,7 +4874,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>7</v>
+        <v>647</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>7</v>
@@ -4818,7 +4923,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>569</v>
+        <v>656</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>57</v>
@@ -4844,10 +4949,10 @@
         <v>58</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>570</v>
+        <v>657</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>571</v>
+        <v>658</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>61</v>
@@ -4873,10 +4978,10 @@
         <v>62</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>572</v>
+        <v>659</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>65</v>
@@ -4902,10 +5007,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>573</v>
+        <v>224</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>574</v>
+        <v>660</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -4934,7 +5039,7 @@
         <v>35</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>575</v>
+        <v>661</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>73</v>
@@ -4963,7 +5068,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>576</v>
+        <v>662</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>77</v>
@@ -4992,7 +5097,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>572</v>
+        <v>663</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>80</v>
@@ -5015,16 +5120,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>49</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>576</v>
+        <v>664</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>7</v>
@@ -5044,7 +5149,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -5053,7 +5158,7 @@
         <v>7</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>7</v>
@@ -5079,7 +5184,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>577</v>
+        <v>665</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>95</v>
@@ -5088,7 +5193,7 @@
         <v>7</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>578</v>
+        <v>7</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>7</v>
@@ -5105,10 +5210,10 @@
         <v>96</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>579</v>
+        <v>666</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>580</v>
+        <v>667</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>99</v>
@@ -5134,16 +5239,16 @@
         <v>100</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>581</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>582</v>
+        <v>668</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>103</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s" s="0">
         <v>7</v>
@@ -5163,10 +5268,10 @@
         <v>104</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>71</v>
+        <v>669</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>583</v>
+        <v>670</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>105</v>
@@ -5192,10 +5297,10 @@
         <v>106</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>584</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>585</v>
+        <v>671</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>109</v>
@@ -5221,10 +5326,10 @@
         <v>111</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>586</v>
+        <v>672</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>113</v>
@@ -5233,7 +5338,7 @@
         <v>7</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>587</v>
+        <v>7</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>7</v>
@@ -5250,10 +5355,10 @@
         <v>114</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>588</v>
+        <v>673</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>116</v>
@@ -5279,10 +5384,10 @@
         <v>117</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>589</v>
+        <v>674</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>119</v>
@@ -5308,10 +5413,10 @@
         <v>120</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>590</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>121</v>
@@ -5334,22 +5439,22 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>7</v>
+        <v>675</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>253</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>7</v>
+        <v>676</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>7</v>
@@ -5363,19 +5468,19 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>7</v>
+        <v>677</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>591</v>
+        <v>678</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F31" t="s" s="0">
         <v>7</v>
@@ -5392,16 +5497,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>592</v>
+        <v>679</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>593</v>
+        <v>680</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>21</v>
@@ -5421,16 +5526,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>594</v>
+        <v>245</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>595</v>
+        <v>681</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>21</v>
@@ -5450,19 +5555,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>596</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>597</v>
+        <v>682</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s" s="0">
         <v>7</v>
@@ -5479,19 +5584,19 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>598</v>
+        <v>683</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>597</v>
+        <v>684</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s" s="0">
         <v>7</v>
@@ -5508,16 +5613,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>591</v>
+        <v>685</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -5537,16 +5642,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>599</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>600</v>
+        <v>686</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -5566,16 +5671,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>601</v>
+        <v>687</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -5595,16 +5700,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>602</v>
+        <v>688</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -5624,16 +5729,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>149</v>
+        <v>208</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s" s="0">
         <v>591</v>
-      </c>
-      <c r="D40" t="s" s="0">
-        <v>151</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -5653,16 +5758,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>603</v>
+        <v>689</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -5677,64 +5782,6 @@
         <v>7</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="0">
-        <v>208</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D42" t="s" s="0">
-        <v>604</v>
-      </c>
-      <c r="E42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I42" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="0">
-        <v>154</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>605</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>156</v>
-      </c>
-      <c r="E43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I43" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -10933,7 +10980,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -10947,19 +10994,19 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="F1" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>3</v>
-      </c>
       <c r="H1" t="s" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s" s="0">
         <v>7</v>
@@ -10973,22 +11020,22 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>7</v>
+        <v>384</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>384</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>7</v>
+        <v>385</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -11002,22 +11049,22 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>7</v>
+        <v>386</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>385</v>
+        <v>7</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>7</v>
+        <v>387</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -11028,25 +11075,25 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>331</v>
+        <v>388</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>332</v>
+        <v>389</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>386</v>
+        <v>7</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -11057,25 +11104,25 @@
         <v>24</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>334</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>387</v>
+        <v>7</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -11086,25 +11133,25 @@
         <v>29</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>71</v>
+        <v>392</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>7</v>
+        <v>395</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -11115,25 +11162,25 @@
         <v>34</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>389</v>
+        <v>7</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>7</v>
+        <v>397</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -11144,13 +11191,13 @@
         <v>39</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>7</v>
@@ -11159,7 +11206,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>7</v>
@@ -11173,13 +11220,13 @@
         <v>44</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>342</v>
+        <v>399</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>7</v>
@@ -11188,7 +11235,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>7</v>
@@ -11202,13 +11249,13 @@
         <v>48</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>7</v>
@@ -11217,7 +11264,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>7</v>
@@ -11231,13 +11278,13 @@
         <v>52</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>344</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>7</v>
@@ -11246,7 +11293,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>7</v>
@@ -11257,25 +11304,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>7</v>
+        <v>385</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>169</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>7</v>
@@ -11286,25 +11327,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>7</v>
+        <v>401</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>7</v>
+        <v>402</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G13" t="s" s="0">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>7</v>
@@ -11315,28 +11350,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>346</v>
+        <v>403</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G14" t="s" s="0">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>7</v>
@@ -11344,28 +11373,22 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>348</v>
+        <v>405</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="F15" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G15" t="s" s="0">
-        <v>65</v>
-      </c>
       <c r="H15" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>7</v>
@@ -11373,25 +11396,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>71</v>
+        <v>407</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>350</v>
+        <v>408</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>7</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G16" t="s" s="0">
-        <v>69</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>7</v>
@@ -11402,25 +11419,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>351</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>7</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G17" t="s" s="0">
-        <v>73</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>7</v>
@@ -11431,25 +11442,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>7</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G18" t="s" s="0">
-        <v>77</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>7</v>
@@ -11460,25 +11465,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>7</v>
-      </c>
-      <c r="F19" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G19" t="s" s="0">
-        <v>80</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>7</v>
@@ -11489,25 +11488,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>355</v>
+        <v>410</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>7</v>
+        <v>412</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>7</v>
-      </c>
-      <c r="F20" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G20" t="s" s="0">
-        <v>83</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>7</v>
@@ -11521,22 +11514,16 @@
         <v>84</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>354</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>7</v>
-      </c>
-      <c r="F21" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G21" t="s" s="0">
-        <v>80</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>7</v>
@@ -11547,25 +11534,25 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>7</v>
+        <v>413</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>7</v>
+        <v>414</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>7</v>
@@ -11576,25 +11563,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>7</v>
+        <v>415</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>7</v>
+        <v>416</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>7</v>
@@ -11605,28 +11592,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>357</v>
+        <v>245</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>358</v>
+        <v>417</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F24" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>7</v>
@@ -11634,16 +11621,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>359</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>7</v>
@@ -11652,10 +11639,10 @@
         <v>7</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>7</v>
@@ -11663,16 +11650,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>245</v>
+        <v>419</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>361</v>
+        <v>420</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>7</v>
@@ -11681,10 +11668,10 @@
         <v>7</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>7</v>
@@ -11692,16 +11679,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>7</v>
@@ -11710,10 +11697,10 @@
         <v>7</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>7</v>
@@ -11721,16 +11708,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>364</v>
+        <v>422</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>7</v>
@@ -11739,7 +11726,7 @@
         <v>7</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>7</v>
@@ -11750,16 +11737,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>365</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>7</v>
@@ -11768,7 +11755,7 @@
         <v>7</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>7</v>
@@ -11779,16 +11766,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>7</v>
@@ -11797,7 +11784,7 @@
         <v>7</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>7</v>
@@ -11808,16 +11795,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>368</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>7</v>
+        <v>253</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>7</v>
@@ -11826,7 +11813,7 @@
         <v>7</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>7</v>
@@ -11837,16 +11824,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>360</v>
+        <v>425</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>7</v>
@@ -11855,7 +11842,7 @@
         <v>7</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>7</v>
@@ -11866,25 +11853,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>254</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>49</v>
+        <v>426</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>369</v>
+        <v>427</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>253</v>
+        <v>7</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>7</v>
@@ -11895,25 +11882,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>370</v>
+        <v>129</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>53</v>
+        <v>428</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>7</v>
+        <v>429</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F34" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>255</v>
+        <v>7</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>7</v>
@@ -11924,25 +11911,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>7</v>
+        <v>430</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>7</v>
+        <v>431</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F35" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>7</v>
@@ -11953,16 +11940,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>372</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -11971,10 +11958,10 @@
         <v>7</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>7</v>
@@ -11982,16 +11969,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>374</v>
+        <v>433</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>375</v>
+        <v>434</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -12000,10 +11987,10 @@
         <v>7</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>132</v>
+        <v>7</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>7</v>
@@ -12011,16 +11998,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>376</v>
+        <v>435</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>7</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -12029,7 +12016,7 @@
         <v>7</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>7</v>
@@ -12040,16 +12027,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>377</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -12058,7 +12045,7 @@
         <v>7</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="H39" t="s" s="0">
         <v>7</v>
@@ -12069,16 +12056,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>379</v>
+        <v>437</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>7</v>
+        <v>151</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -12087,7 +12074,7 @@
         <v>7</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="H40" t="s" s="0">
         <v>7</v>
@@ -12098,16 +12085,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>380</v>
+        <v>436</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -12116,7 +12103,7 @@
         <v>7</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>145</v>
+        <v>7</v>
       </c>
       <c r="H41" t="s" s="0">
         <v>7</v>
@@ -12127,16 +12114,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>381</v>
+        <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>7</v>
+        <v>153</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -12145,7 +12132,7 @@
         <v>7</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="H42" t="s" s="0">
         <v>7</v>
@@ -12156,16 +12143,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>149</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>7</v>
+        <v>156</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -12174,7 +12158,7 @@
         <v>7</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="H43" t="s" s="0">
         <v>7</v>
@@ -12184,15 +12168,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s" s="0">
-        <v>152</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C44" t="s" s="0">
-        <v>7</v>
-      </c>
       <c r="D44" t="s" s="0">
         <v>7</v>
       </c>
@@ -12203,41 +12178,12 @@
         <v>7</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="H44" t="s" s="0">
         <v>7</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="0">
-        <v>154</v>
-      </c>
-      <c r="B45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C45" t="s" s="0">
-        <v>383</v>
-      </c>
-      <c r="D45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G45" t="s" s="0">
-        <v>156</v>
-      </c>
-      <c r="H45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I45" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12248,7 +12194,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -12288,16 +12234,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>7</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>7</v>
+        <v>440</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>10</v>
@@ -12317,7 +12263,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>7</v>
+        <v>442</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>7</v>
@@ -12326,7 +12272,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>392</v>
+        <v>212</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>15</v>
@@ -12343,10 +12289,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>331</v>
+        <v>443</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>332</v>
+        <v>444</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>7</v>
@@ -12355,7 +12301,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>393</v>
+        <v>445</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>20</v>
@@ -12372,10 +12318,10 @@
         <v>24</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>334</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>335</v>
+        <v>446</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>7</v>
@@ -12384,13 +12330,13 @@
         <v>7</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>27</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -12401,10 +12347,10 @@
         <v>29</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>71</v>
+        <v>448</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>337</v>
+        <v>449</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>7</v>
@@ -12413,7 +12359,7 @@
         <v>7</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>395</v>
+        <v>450</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>32</v>
@@ -12430,10 +12376,10 @@
         <v>34</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>337</v>
+        <v>451</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>7</v>
@@ -12442,7 +12388,7 @@
         <v>7</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>396</v>
+        <v>452</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>37</v>
@@ -12459,10 +12405,10 @@
         <v>39</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>341</v>
+        <v>453</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>7</v>
@@ -12488,10 +12434,10 @@
         <v>44</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>342</v>
+        <v>454</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>7</v>
@@ -12517,10 +12463,10 @@
         <v>48</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>343</v>
+        <v>455</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>7</v>
@@ -12546,10 +12492,10 @@
         <v>52</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>344</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>7</v>
@@ -12572,13 +12518,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>7</v>
+        <v>456</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>7</v>
@@ -12590,7 +12536,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>169</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>7</v>
@@ -12601,13 +12547,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>7</v>
+        <v>457</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>7</v>
+        <v>458</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>7</v>
@@ -12619,10 +12565,10 @@
         <v>7</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>7</v>
@@ -12630,13 +12576,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>346</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>347</v>
+        <v>456</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>7</v>
@@ -12648,10 +12594,10 @@
         <v>7</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>7</v>
@@ -12659,13 +12605,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>348</v>
+        <v>459</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>349</v>
+        <v>460</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>7</v>
@@ -12677,10 +12623,10 @@
         <v>7</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>7</v>
@@ -12688,13 +12634,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>350</v>
+        <v>461</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>7</v>
@@ -12706,7 +12652,7 @@
         <v>7</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>7</v>
@@ -12717,13 +12663,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>351</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>352</v>
+        <v>462</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>7</v>
@@ -12735,7 +12681,7 @@
         <v>7</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>7</v>
@@ -12746,13 +12692,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>353</v>
+        <v>463</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>7</v>
@@ -12764,7 +12710,7 @@
         <v>7</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>7</v>
@@ -12775,13 +12721,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>354</v>
+        <v>464</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>7</v>
@@ -12793,7 +12739,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>7</v>
@@ -12804,13 +12750,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>355</v>
+        <v>7</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>7</v>
@@ -12822,7 +12768,7 @@
         <v>7</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>7</v>
@@ -12833,13 +12779,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>49</v>
+        <v>465</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>354</v>
+        <v>466</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>7</v>
@@ -12851,7 +12797,7 @@
         <v>7</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>7</v>
@@ -12862,13 +12808,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>7</v>
+        <v>467</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>7</v>
@@ -12880,10 +12826,10 @@
         <v>7</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>7</v>
@@ -12891,13 +12837,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>7</v>
+        <v>468</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>7</v>
@@ -12909,10 +12855,10 @@
         <v>7</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>7</v>
@@ -12920,13 +12866,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>357</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>358</v>
+        <v>469</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>7</v>
@@ -12938,10 +12884,10 @@
         <v>7</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>7</v>
@@ -12949,13 +12895,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>359</v>
+        <v>470</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>7</v>
@@ -12967,10 +12913,10 @@
         <v>7</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>7</v>
@@ -12978,13 +12924,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>361</v>
+        <v>472</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>7</v>
@@ -12996,10 +12942,10 @@
         <v>7</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>7</v>
@@ -13007,13 +12953,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>362</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>363</v>
+        <v>473</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>7</v>
@@ -13025,10 +12971,10 @@
         <v>7</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>7</v>
@@ -13036,13 +12982,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>364</v>
+        <v>474</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>7</v>
@@ -13054,7 +13000,7 @@
         <v>7</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>7</v>
@@ -13065,13 +13011,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>365</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>366</v>
+        <v>473</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>7</v>
@@ -13083,7 +13029,7 @@
         <v>7</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>7</v>
@@ -13094,13 +13040,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>367</v>
+        <v>7</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>7</v>
@@ -13112,7 +13058,7 @@
         <v>7</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>7</v>
@@ -13123,13 +13069,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>368</v>
+        <v>475</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>7</v>
@@ -13141,7 +13087,7 @@
         <v>7</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>7</v>
@@ -13152,13 +13098,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>45</v>
+        <v>476</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>360</v>
+        <v>477</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>7</v>
@@ -13170,10 +13116,10 @@
         <v>7</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>7</v>
@@ -13181,13 +13127,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>254</v>
+        <v>129</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>49</v>
+        <v>478</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>369</v>
+        <v>479</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>7</v>
@@ -13199,10 +13145,10 @@
         <v>7</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>253</v>
+        <v>132</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>7</v>
@@ -13210,13 +13156,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>370</v>
+        <v>133</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>7</v>
+        <v>480</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>7</v>
@@ -13228,7 +13174,7 @@
         <v>7</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>255</v>
+        <v>135</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>7</v>
@@ -13239,13 +13185,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>7</v>
+        <v>481</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>7</v>
+        <v>482</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>7</v>
@@ -13257,7 +13203,7 @@
         <v>7</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>7</v>
@@ -13268,13 +13214,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>372</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>373</v>
+        <v>483</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>7</v>
@@ -13286,10 +13232,10 @@
         <v>7</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>7</v>
@@ -13297,13 +13243,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>374</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>375</v>
+        <v>484</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>7</v>
@@ -13315,10 +13261,10 @@
         <v>7</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>7</v>
@@ -13326,13 +13272,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>376</v>
+        <v>485</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>7</v>
@@ -13344,7 +13290,7 @@
         <v>7</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>7</v>
@@ -13355,13 +13301,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>377</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>378</v>
+        <v>486</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>7</v>
@@ -13373,7 +13319,7 @@
         <v>7</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="H39" t="s" s="0">
         <v>7</v>
@@ -13384,13 +13330,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>379</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>7</v>
@@ -13402,7 +13348,7 @@
         <v>7</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H40" t="s" s="0">
         <v>7</v>
@@ -13413,13 +13359,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>380</v>
+        <v>487</v>
       </c>
       <c r="D41" t="s" s="0">
         <v>7</v>
@@ -13431,128 +13377,12 @@
         <v>7</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="H41" t="s" s="0">
         <v>7</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="C42" t="s" s="0">
-        <v>381</v>
-      </c>
-      <c r="D42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G42" t="s" s="0">
-        <v>148</v>
-      </c>
-      <c r="H42" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I42" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="0">
-        <v>149</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>382</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G43" t="s" s="0">
-        <v>151</v>
-      </c>
-      <c r="H43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I43" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="0">
-        <v>152</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G44" t="s" s="0">
-        <v>153</v>
-      </c>
-      <c r="H44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I44" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="0">
-        <v>154</v>
-      </c>
-      <c r="B45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C45" t="s" s="0">
-        <v>383</v>
-      </c>
-      <c r="D45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G45" t="s" s="0">
-        <v>156</v>
-      </c>
-      <c r="H45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I45" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13563,7 +13393,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -13603,7 +13433,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>397</v>
+        <v>488</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -13612,13 +13442,13 @@
         <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>7</v>
+        <v>489</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>398</v>
+        <v>490</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -13632,7 +13462,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>399</v>
+        <v>491</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -13644,10 +13474,10 @@
         <v>7</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>7</v>
+        <v>492</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>400</v>
+        <v>493</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -13658,10 +13488,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>401</v>
+        <v>494</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>402</v>
+        <v>495</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -13676,7 +13506,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>259</v>
+        <v>496</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -13687,16 +13517,16 @@
         <v>24</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>71</v>
+        <v>497</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>403</v>
+        <v>498</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>27</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>7</v>
@@ -13705,7 +13535,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>404</v>
+        <v>499</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -13716,10 +13546,10 @@
         <v>29</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>405</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>406</v>
+        <v>500</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>32</v>
@@ -13728,13 +13558,13 @@
         <v>7</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>407</v>
+        <v>7</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -13745,10 +13575,10 @@
         <v>34</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>35</v>
+        <v>502</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>409</v>
+        <v>503</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>37</v>
@@ -13763,7 +13593,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>410</v>
+        <v>504</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -13774,10 +13604,10 @@
         <v>39</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>411</v>
+        <v>505</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>42</v>
@@ -13789,9 +13619,6 @@
         <v>7</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H8" t="s" s="0">
         <v>7</v>
       </c>
       <c r="I8" t="s" s="0">
@@ -13803,10 +13630,10 @@
         <v>44</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>412</v>
+        <v>506</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>47</v>
@@ -13832,10 +13659,10 @@
         <v>48</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>413</v>
+        <v>507</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>51</v>
@@ -13861,10 +13688,10 @@
         <v>52</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>54</v>
@@ -13887,18 +13714,24 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>55</v>
+        <v>168</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>398</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="E12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G12" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H12" t="s" s="0">
@@ -13910,19 +13743,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>414</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>415</v>
+        <v>509</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>7</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>7</v>
@@ -13933,20 +13772,26 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>416</v>
+        <v>510</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>417</v>
+        <v>511</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>21</v>
       </c>
+      <c r="F14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>7</v>
+      </c>
       <c r="H14" t="s" s="0">
         <v>7</v>
       </c>
@@ -13956,18 +13801,24 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>418</v>
+        <v>512</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>419</v>
+        <v>513</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G15" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H15" t="s" s="0">
@@ -13979,18 +13830,24 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>421</v>
+        <v>514</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G16" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H16" t="s" s="0">
@@ -14002,18 +13859,24 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>35</v>
+        <v>515</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>422</v>
+        <v>516</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G17" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H17" t="s" s="0">
@@ -14025,18 +13888,24 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>423</v>
+        <v>517</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G18" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H18" t="s" s="0">
@@ -14048,18 +13917,24 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>424</v>
+        <v>518</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G19" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H19" t="s" s="0">
@@ -14071,18 +13946,24 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>423</v>
+        <v>519</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G20" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H20" t="s" s="0">
@@ -14097,10 +13978,10 @@
         <v>84</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>7</v>
+        <v>520</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>86</v>
@@ -14108,6 +13989,12 @@
       <c r="E21" t="s" s="0">
         <v>7</v>
       </c>
+      <c r="F21" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>7</v>
+      </c>
       <c r="H21" t="s" s="0">
         <v>7</v>
       </c>
@@ -14117,22 +14004,22 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>426</v>
+        <v>7</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>427</v>
+        <v>7</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>7</v>
@@ -14146,19 +14033,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>428</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>429</v>
+        <v>521</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s" s="0">
         <v>7</v>
@@ -14175,16 +14062,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>245</v>
+        <v>522</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>430</v>
+        <v>523</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>21</v>
@@ -14204,19 +14091,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>25</v>
+        <v>524</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>431</v>
+        <v>525</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s" s="0">
         <v>7</v>
@@ -14233,19 +14120,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>432</v>
+        <v>303</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>433</v>
+        <v>526</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F26" t="s" s="0">
         <v>7</v>
@@ -14262,16 +14149,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>434</v>
+        <v>527</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>7</v>
@@ -14291,16 +14178,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>40</v>
+        <v>528</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>435</v>
+        <v>529</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>7</v>
@@ -14320,16 +14207,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>436</v>
+        <v>530</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>7</v>
@@ -14349,16 +14236,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>437</v>
+        <v>531</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>7</v>
@@ -14378,16 +14265,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>7</v>
+        <v>527</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>253</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>7</v>
@@ -14407,16 +14294,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>122</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>438</v>
+        <v>532</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>124</v>
+        <v>253</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>7</v>
@@ -14436,19 +14323,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>125</v>
+        <v>254</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>439</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>440</v>
+        <v>7</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>128</v>
+        <v>255</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F33" t="s" s="0">
         <v>7</v>
@@ -14465,19 +14352,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>441</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>442</v>
+        <v>533</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s" s="0">
         <v>7</v>
@@ -14494,16 +14381,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>443</v>
+        <v>301</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>444</v>
+        <v>534</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>21</v>
@@ -14523,16 +14410,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>25</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>445</v>
+        <v>535</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -14552,16 +14439,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>446</v>
+        <v>306</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>447</v>
+        <v>536</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -14581,16 +14468,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>448</v>
+        <v>537</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -14610,16 +14497,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>40</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>449</v>
+        <v>309</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -14639,16 +14526,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>45</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>450</v>
+        <v>538</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -14674,7 +14561,7 @@
         <v>49</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>449</v>
+        <v>311</v>
       </c>
       <c r="D41" t="s" s="0">
         <v>148</v>
@@ -14697,7 +14584,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>53</v>
@@ -14706,7 +14593,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -14728,8 +14615,11 @@
       <c r="A43" t="s" s="0">
         <v>154</v>
       </c>
+      <c r="B43" t="s" s="0">
+        <v>7</v>
+      </c>
       <c r="C43" t="s" s="0">
-        <v>451</v>
+        <v>539</v>
       </c>
       <c r="D43" t="s" s="0">
         <v>156</v>
@@ -14747,26 +14637,6 @@
         <v>7</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="D44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="H44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I44" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -14777,7 +14647,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -14791,19 +14661,19 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="F1" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>3</v>
-      </c>
       <c r="H1" t="s" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s" s="0">
         <v>7</v>
@@ -14817,22 +14687,22 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>452</v>
+        <v>540</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>453</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>454</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>10</v>
+        <v>541</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>7</v>
+        <v>542</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -14846,22 +14716,22 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>455</v>
+        <v>543</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>212</v>
+        <v>7</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>7</v>
+        <v>544</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -14872,25 +14742,25 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>456</v>
+        <v>545</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>457</v>
+        <v>546</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>458</v>
+        <v>7</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>21</v>
+        <v>547</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -14904,22 +14774,22 @@
         <v>25</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>459</v>
+        <v>548</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>460</v>
+        <v>7</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>7</v>
+        <v>549</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -14930,25 +14800,25 @@
         <v>29</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>462</v>
+        <v>550</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>463</v>
+        <v>7</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>7</v>
+        <v>551</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -14962,22 +14832,22 @@
         <v>35</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>465</v>
+        <v>7</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>7</v>
+        <v>552</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -14991,10 +14861,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>466</v>
+        <v>553</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>7</v>
@@ -15003,7 +14873,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>7</v>
@@ -15020,10 +14890,10 @@
         <v>45</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>467</v>
+        <v>554</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>7</v>
@@ -15032,7 +14902,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>7</v>
@@ -15049,10 +14919,10 @@
         <v>49</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>468</v>
+        <v>555</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>7</v>
@@ -15061,7 +14931,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>7</v>
@@ -15081,7 +14951,7 @@
         <v>7</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>7</v>
@@ -15090,7 +14960,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>7</v>
@@ -15107,10 +14977,10 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>469</v>
+        <v>556</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -15119,7 +14989,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>7</v>
@@ -15133,25 +15003,25 @@
         <v>58</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>470</v>
+        <v>557</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>471</v>
+        <v>558</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>7</v>
@@ -15162,13 +15032,13 @@
         <v>62</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>469</v>
+        <v>559</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>7</v>
@@ -15177,7 +15047,7 @@
         <v>7</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>7</v>
@@ -15191,13 +15061,13 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>472</v>
+        <v>560</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>473</v>
+        <v>561</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>7</v>
@@ -15206,7 +15076,7 @@
         <v>7</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>7</v>
@@ -15223,10 +15093,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>474</v>
+        <v>562</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>7</v>
@@ -15235,7 +15105,7 @@
         <v>7</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>7</v>
@@ -15252,10 +15122,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>475</v>
+        <v>563</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>7</v>
@@ -15264,7 +15134,7 @@
         <v>7</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>7</v>
@@ -15281,10 +15151,10 @@
         <v>45</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>476</v>
+        <v>559</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>7</v>
@@ -15293,7 +15163,7 @@
         <v>7</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>7</v>
@@ -15304,16 +15174,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>49</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>477</v>
+        <v>563</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>7</v>
@@ -15322,7 +15192,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>7</v>
@@ -15333,7 +15203,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -15342,7 +15212,7 @@
         <v>7</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>7</v>
@@ -15351,7 +15221,7 @@
         <v>7</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>7</v>
@@ -15365,22 +15235,22 @@
         <v>93</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>478</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>479</v>
+        <v>564</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>7</v>
+        <v>565</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>7</v>
@@ -15394,25 +15264,25 @@
         <v>96</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>101</v>
+        <v>566</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>480</v>
+        <v>567</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>7</v>
@@ -15423,25 +15293,25 @@
         <v>100</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>97</v>
+        <v>568</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>481</v>
+        <v>569</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>7</v>
@@ -15455,10 +15325,10 @@
         <v>71</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>482</v>
+        <v>570</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>7</v>
@@ -15467,7 +15337,7 @@
         <v>7</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>7</v>
@@ -15481,13 +15351,13 @@
         <v>106</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>483</v>
+        <v>571</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>484</v>
+        <v>572</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>7</v>
@@ -15496,7 +15366,7 @@
         <v>7</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>7</v>
@@ -15513,19 +15383,19 @@
         <v>35</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>485</v>
+        <v>573</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>7</v>
+        <v>574</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>7</v>
@@ -15542,10 +15412,10 @@
         <v>40</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>486</v>
+        <v>575</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>7</v>
@@ -15554,7 +15424,7 @@
         <v>7</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>7</v>
@@ -15571,10 +15441,10 @@
         <v>45</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>487</v>
+        <v>576</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>7</v>
@@ -15583,7 +15453,7 @@
         <v>7</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>7</v>
@@ -15600,10 +15470,10 @@
         <v>49</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>486</v>
+        <v>577</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>7</v>
@@ -15612,7 +15482,7 @@
         <v>7</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>7</v>
@@ -15632,7 +15502,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>7</v>
+        <v>253</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>7</v>
@@ -15641,7 +15511,7 @@
         <v>7</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>7</v>
@@ -15658,10 +15528,10 @@
         <v>7</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>488</v>
+        <v>578</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>7</v>
@@ -15670,7 +15540,7 @@
         <v>7</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>7</v>
@@ -15684,25 +15554,25 @@
         <v>125</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>489</v>
+        <v>579</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>490</v>
+        <v>580</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F32" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>7</v>
@@ -15713,25 +15583,25 @@
         <v>129</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>491</v>
+        <v>581</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>492</v>
+        <v>582</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>132</v>
+        <v>7</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>7</v>
@@ -15742,22 +15612,22 @@
         <v>133</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>25</v>
+        <v>583</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>493</v>
+        <v>584</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F34" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>7</v>
@@ -15768,25 +15638,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>494</v>
+        <v>585</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>495</v>
+        <v>584</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F35" t="s" s="0">
         <v>7</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>7</v>
@@ -15797,16 +15667,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>496</v>
+        <v>578</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -15815,7 +15685,7 @@
         <v>7</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>142</v>
+        <v>7</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>7</v>
@@ -15826,16 +15696,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>40</v>
+        <v>586</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>497</v>
+        <v>587</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -15844,7 +15714,7 @@
         <v>7</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>145</v>
+        <v>7</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>7</v>
@@ -15855,16 +15725,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>498</v>
+        <v>588</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>7</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -15873,7 +15743,7 @@
         <v>7</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>7</v>
@@ -15884,16 +15754,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>499</v>
+        <v>589</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -15902,7 +15772,7 @@
         <v>7</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="H39" t="s" s="0">
         <v>7</v>
@@ -15913,16 +15783,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>7</v>
+        <v>578</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>7</v>
+        <v>151</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -15931,7 +15801,7 @@
         <v>7</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="H40" t="s" s="0">
         <v>7</v>
@@ -15942,30 +15812,88 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="H41" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="I41" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>591</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G42" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="H42" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="I42" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
         <v>154</v>
       </c>
-      <c r="B41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C41" t="s" s="0">
-        <v>500</v>
-      </c>
-      <c r="D41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="E41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G41" t="s" s="0">
+      <c r="B43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>592</v>
+      </c>
+      <c r="D43" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="H41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I41" t="s" s="0">
+      <c r="E43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="H43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="I43" t="s" s="0">
         <v>7</v>
       </c>
     </row>

--- a/src/main/java/video/call/data/topics.xlsx
+++ b/src/main/java/video/call/data/topics.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4231" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4108" uniqueCount="684">
   <si>
     <t>Part</t>
   </si>
@@ -1344,12 +1344,6 @@
     <t>Hi! It's good to see you again. Look! I have a plant.</t>
   </si>
   <si>
-    <t>a sunflower plant</t>
-  </si>
-  <si>
-    <t>I have a small plant.</t>
-  </si>
-  <si>
     <t>Do you know what it is?</t>
   </si>
   <si>
@@ -1359,28 +1353,16 @@
     <t xml:space="preserve">Yeah. You got it right. It's a sunflower. </t>
   </si>
   <si>
-    <t>It's a sunflower.</t>
-  </si>
-  <si>
     <t>Take a closer look. What plant is it?</t>
   </si>
   <si>
-    <t>Does it grow tall?</t>
-  </si>
-  <si>
     <t>User asks: What it is?</t>
   </si>
   <si>
     <t>A sunflower. Can you say "It's a sunflower."?</t>
   </si>
   <si>
-    <t>Yes, very tall!</t>
-  </si>
-  <si>
     <t>Can you speak louder, please. What is it?</t>
-  </si>
-  <si>
-    <t>I want a sunflower, too.</t>
   </si>
   <si>
     <t>Let me help you. It's a sunflower.</t>
@@ -3527,7 +3509,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -3539,10 +3521,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -3556,7 +3538,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -3571,7 +3553,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -3582,10 +3564,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -3600,7 +3582,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -3611,10 +3593,10 @@
         <v>24</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>27</v>
@@ -3629,7 +3611,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -3640,10 +3622,10 @@
         <v>24</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>27</v>
@@ -3658,7 +3640,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -3672,7 +3654,7 @@
         <v>218</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>27</v>
@@ -3687,7 +3669,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -3701,7 +3683,7 @@
         <v>221</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>32</v>
@@ -3716,7 +3698,7 @@
         <v>7</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>7</v>
@@ -3727,10 +3709,10 @@
         <v>24</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>27</v>
@@ -3756,7 +3738,7 @@
         <v>35</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>37</v>
@@ -3782,7 +3764,7 @@
         <v>40</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>42</v>
@@ -3811,7 +3793,7 @@
         <v>45</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>47</v>
@@ -3840,7 +3822,7 @@
         <v>49</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>27</v>
@@ -3892,13 +3874,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>57</v>
@@ -3924,10 +3906,10 @@
         <v>58</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>61</v>
@@ -3953,10 +3935,10 @@
         <v>62</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>65</v>
@@ -3982,10 +3964,10 @@
         <v>66</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>69</v>
@@ -4011,10 +3993,10 @@
         <v>70</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>73</v>
@@ -4040,10 +4022,10 @@
         <v>66</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>69</v>
@@ -4072,7 +4054,7 @@
         <v>221</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>77</v>
@@ -4098,10 +4080,10 @@
         <v>78</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>80</v>
@@ -4130,7 +4112,7 @@
         <v>35</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>83</v>
@@ -4159,7 +4141,7 @@
         <v>40</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>86</v>
@@ -4188,7 +4170,7 @@
         <v>45</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>90</v>
@@ -4217,7 +4199,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>86</v>
@@ -4275,7 +4257,7 @@
         <v>7</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>95</v>
@@ -4301,10 +4283,10 @@
         <v>96</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>99</v>
@@ -4330,10 +4312,10 @@
         <v>100</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>103</v>
@@ -4362,7 +4344,7 @@
         <v>71</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>105</v>
@@ -4388,10 +4370,10 @@
         <v>106</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>109</v>
@@ -4420,7 +4402,7 @@
         <v>35</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>113</v>
@@ -4449,7 +4431,7 @@
         <v>40</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>116</v>
@@ -4478,7 +4460,7 @@
         <v>45</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>119</v>
@@ -4507,7 +4489,7 @@
         <v>49</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>116</v>
@@ -4565,7 +4547,7 @@
         <v>7</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>156</v>
@@ -4633,7 +4615,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -4645,10 +4627,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -4662,7 +4644,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -4677,7 +4659,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -4688,10 +4670,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -4700,13 +4682,13 @@
         <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -4720,7 +4702,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>27</v>
@@ -4735,7 +4717,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -4746,10 +4728,10 @@
         <v>29</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>32</v>
@@ -4764,7 +4746,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -4778,7 +4760,7 @@
         <v>35</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>37</v>
@@ -4793,7 +4775,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -4807,7 +4789,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>42</v>
@@ -4816,7 +4798,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>7</v>
@@ -4836,7 +4818,7 @@
         <v>45</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>47</v>
@@ -4865,7 +4847,7 @@
         <v>49</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>51</v>
@@ -4874,7 +4856,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>7</v>
@@ -4923,7 +4905,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>57</v>
@@ -4949,10 +4931,10 @@
         <v>58</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>61</v>
@@ -4981,7 +4963,7 @@
         <v>71</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>65</v>
@@ -5010,7 +4992,7 @@
         <v>224</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -5039,7 +5021,7 @@
         <v>35</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>73</v>
@@ -5068,7 +5050,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>77</v>
@@ -5097,7 +5079,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>80</v>
@@ -5126,7 +5108,7 @@
         <v>49</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>83</v>
@@ -5184,7 +5166,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>95</v>
@@ -5210,10 +5192,10 @@
         <v>96</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>99</v>
@@ -5242,7 +5224,7 @@
         <v>71</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>103</v>
@@ -5268,10 +5250,10 @@
         <v>104</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>105</v>
@@ -5300,7 +5282,7 @@
         <v>35</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>109</v>
@@ -5329,7 +5311,7 @@
         <v>40</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>113</v>
@@ -5358,7 +5340,7 @@
         <v>45</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>116</v>
@@ -5387,7 +5369,7 @@
         <v>49</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>119</v>
@@ -5445,7 +5427,7 @@
         <v>7</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>124</v>
@@ -5454,7 +5436,7 @@
         <v>7</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>7</v>
@@ -5471,10 +5453,10 @@
         <v>125</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>128</v>
@@ -5500,10 +5482,10 @@
         <v>129</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>132</v>
@@ -5532,7 +5514,7 @@
         <v>245</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>135</v>
@@ -5561,7 +5543,7 @@
         <v>25</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>139</v>
@@ -5587,10 +5569,10 @@
         <v>140</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>142</v>
@@ -5619,7 +5601,7 @@
         <v>35</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>145</v>
@@ -5648,7 +5630,7 @@
         <v>40</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>148</v>
@@ -5677,7 +5659,7 @@
         <v>45</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>151</v>
@@ -5706,7 +5688,7 @@
         <v>49</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>153</v>
@@ -5738,7 +5720,7 @@
         <v>7</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -5764,7 +5746,7 @@
         <v>7</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="D41" t="s" s="0">
         <v>156</v>
@@ -12194,7 +12176,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -12208,21 +12190,12 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12237,21 +12210,12 @@
         <v>439</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>440</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>441</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I2" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12263,24 +12227,15 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>212</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I3" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12289,27 +12244,18 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>445</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12321,24 +12267,15 @@
         <v>25</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>447</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I5" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12347,27 +12284,18 @@
         <v>29</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>450</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I6" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12379,24 +12307,15 @@
         <v>35</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>452</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I7" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12408,24 +12327,15 @@
         <v>40</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I8" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12437,24 +12347,15 @@
         <v>45</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="H9" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I9" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12466,24 +12367,15 @@
         <v>49</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I10" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12498,21 +12390,12 @@
         <v>7</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="H11" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I11" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12524,24 +12407,15 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>57</v>
-      </c>
-      <c r="H12" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I12" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12550,27 +12424,18 @@
         <v>58</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G13" t="s" s="0">
-        <v>61</v>
-      </c>
-      <c r="H13" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="I13" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12582,24 +12447,15 @@
         <v>71</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G14" t="s" s="0">
-        <v>65</v>
-      </c>
-      <c r="H14" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I14" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12608,27 +12464,18 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G15" t="s" s="0">
-        <v>69</v>
-      </c>
-      <c r="H15" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I15" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12640,24 +12487,15 @@
         <v>35</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G16" t="s" s="0">
-        <v>73</v>
-      </c>
-      <c r="H16" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I16" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12669,24 +12507,15 @@
         <v>40</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G17" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="H17" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I17" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12698,24 +12527,15 @@
         <v>45</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G18" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="H18" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I18" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12727,24 +12547,15 @@
         <v>49</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G19" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="H19" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I19" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12759,21 +12570,12 @@
         <v>7</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G20" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="H20" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I20" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12782,27 +12584,18 @@
         <v>93</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G21" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="H21" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I21" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12814,24 +12607,15 @@
         <v>101</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G22" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="H22" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="I22" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12843,24 +12627,15 @@
         <v>97</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G23" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="H23" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="I23" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12872,24 +12647,15 @@
         <v>71</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G24" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="H24" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I24" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12898,27 +12664,18 @@
         <v>106</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G25" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="H25" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I25" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12930,24 +12687,15 @@
         <v>35</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G26" t="s" s="0">
-        <v>113</v>
-      </c>
-      <c r="H26" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I26" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12959,24 +12707,15 @@
         <v>40</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G27" t="s" s="0">
-        <v>116</v>
-      </c>
-      <c r="H27" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I27" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -12988,24 +12727,15 @@
         <v>45</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G28" t="s" s="0">
-        <v>119</v>
-      </c>
-      <c r="H28" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I28" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13017,24 +12747,15 @@
         <v>49</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G29" t="s" s="0">
-        <v>116</v>
-      </c>
-      <c r="H29" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I29" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13049,21 +12770,12 @@
         <v>7</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G30" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="H30" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I30" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13075,24 +12787,15 @@
         <v>7</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G31" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="H31" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I31" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13101,27 +12804,18 @@
         <v>125</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G32" t="s" s="0">
-        <v>128</v>
-      </c>
-      <c r="H32" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="I32" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13130,27 +12824,18 @@
         <v>129</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G33" t="s" s="0">
-        <v>132</v>
-      </c>
-      <c r="H33" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="I33" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13162,24 +12847,15 @@
         <v>25</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G34" t="s" s="0">
-        <v>135</v>
-      </c>
-      <c r="H34" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I34" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13188,27 +12864,18 @@
         <v>136</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G35" t="s" s="0">
-        <v>139</v>
-      </c>
-      <c r="H35" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I35" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13220,24 +12887,15 @@
         <v>35</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G36" t="s" s="0">
-        <v>142</v>
-      </c>
-      <c r="H36" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I36" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13249,24 +12907,15 @@
         <v>40</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>7</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G37" t="s" s="0">
-        <v>145</v>
-      </c>
-      <c r="H37" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I37" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13278,24 +12927,15 @@
         <v>45</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G38" t="s" s="0">
-        <v>148</v>
-      </c>
-      <c r="H38" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I38" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13307,24 +12947,15 @@
         <v>49</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>7</v>
+        <v>151</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G39" t="s" s="0">
-        <v>151</v>
-      </c>
-      <c r="H39" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I39" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13339,21 +12970,12 @@
         <v>7</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>7</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G40" t="s" s="0">
-        <v>153</v>
-      </c>
-      <c r="H40" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I40" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13365,24 +12987,15 @@
         <v>7</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>7</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G41" t="s" s="0">
-        <v>156</v>
-      </c>
-      <c r="H41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="I41" t="s" s="0">
         <v>7</v>
       </c>
     </row>
@@ -13433,7 +13046,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -13442,13 +13055,13 @@
         <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -13462,7 +13075,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -13474,10 +13087,10 @@
         <v>7</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -13488,10 +13101,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -13506,7 +13119,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -13517,10 +13130,10 @@
         <v>24</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>27</v>
@@ -13535,7 +13148,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -13549,7 +13162,7 @@
         <v>71</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>32</v>
@@ -13564,7 +13177,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -13575,10 +13188,10 @@
         <v>34</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>37</v>
@@ -13593,7 +13206,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -13607,7 +13220,7 @@
         <v>35</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>42</v>
@@ -13633,7 +13246,7 @@
         <v>40</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>47</v>
@@ -13662,7 +13275,7 @@
         <v>45</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>51</v>
@@ -13691,7 +13304,7 @@
         <v>49</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>54</v>
@@ -13749,7 +13362,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>57</v>
@@ -13775,10 +13388,10 @@
         <v>58</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>61</v>
@@ -13804,10 +13417,10 @@
         <v>62</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>65</v>
@@ -13836,7 +13449,7 @@
         <v>25</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -13862,10 +13475,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>73</v>
@@ -13894,7 +13507,7 @@
         <v>35</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>77</v>
@@ -13923,7 +13536,7 @@
         <v>40</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>80</v>
@@ -13952,7 +13565,7 @@
         <v>45</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>83</v>
@@ -13981,7 +13594,7 @@
         <v>49</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>86</v>
@@ -14039,7 +13652,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>95</v>
@@ -14065,10 +13678,10 @@
         <v>96</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>99</v>
@@ -14094,10 +13707,10 @@
         <v>100</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>103</v>
@@ -14126,7 +13739,7 @@
         <v>303</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>105</v>
@@ -14155,7 +13768,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>109</v>
@@ -14181,10 +13794,10 @@
         <v>111</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>113</v>
@@ -14213,7 +13826,7 @@
         <v>35</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>116</v>
@@ -14242,7 +13855,7 @@
         <v>40</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>119</v>
@@ -14271,7 +13884,7 @@
         <v>45</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>121</v>
@@ -14300,7 +13913,7 @@
         <v>49</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>253</v>
@@ -14358,7 +13971,7 @@
         <v>7</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>124</v>
@@ -14387,7 +14000,7 @@
         <v>301</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>128</v>
@@ -14416,7 +14029,7 @@
         <v>25</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>132</v>
@@ -14445,7 +14058,7 @@
         <v>306</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>135</v>
@@ -14474,7 +14087,7 @@
         <v>35</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>139</v>
@@ -14532,7 +14145,7 @@
         <v>45</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>145</v>
@@ -14619,7 +14232,7 @@
         <v>7</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D43" t="s" s="0">
         <v>156</v>
@@ -14687,7 +14300,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -14699,10 +14312,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -14716,7 +14329,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -14731,7 +14344,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -14742,10 +14355,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -14760,7 +14373,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -14774,7 +14387,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>27</v>
@@ -14789,7 +14402,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -14800,10 +14413,10 @@
         <v>29</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>32</v>
@@ -14818,7 +14431,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -14832,7 +14445,7 @@
         <v>35</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>37</v>
@@ -14847,7 +14460,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -14861,7 +14474,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>42</v>
@@ -14890,7 +14503,7 @@
         <v>45</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>47</v>
@@ -14919,7 +14532,7 @@
         <v>49</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>51</v>
@@ -14977,7 +14590,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>57</v>
@@ -15003,10 +14616,10 @@
         <v>58</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>61</v>
@@ -15035,7 +14648,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>65</v>
@@ -15061,10 +14674,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -15093,7 +14706,7 @@
         <v>35</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>73</v>
@@ -15122,7 +14735,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>77</v>
@@ -15151,7 +14764,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>80</v>
@@ -15180,7 +14793,7 @@
         <v>49</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>77</v>
@@ -15238,7 +14851,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>95</v>
@@ -15247,7 +14860,7 @@
         <v>7</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>7</v>
@@ -15264,10 +14877,10 @@
         <v>96</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>99</v>
@@ -15293,10 +14906,10 @@
         <v>100</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>103</v>
@@ -15325,7 +14938,7 @@
         <v>71</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>105</v>
@@ -15351,10 +14964,10 @@
         <v>106</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>109</v>
@@ -15383,7 +14996,7 @@
         <v>35</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>113</v>
@@ -15392,7 +15005,7 @@
         <v>7</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>7</v>
@@ -15412,7 +15025,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>116</v>
@@ -15441,7 +15054,7 @@
         <v>45</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>119</v>
@@ -15470,7 +15083,7 @@
         <v>49</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>121</v>
@@ -15528,7 +15141,7 @@
         <v>7</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>124</v>
@@ -15554,10 +15167,10 @@
         <v>125</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>128</v>
@@ -15583,10 +15196,10 @@
         <v>129</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>132</v>
@@ -15612,10 +15225,10 @@
         <v>133</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>135</v>
@@ -15641,10 +15254,10 @@
         <v>133</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>135</v>
@@ -15673,7 +15286,7 @@
         <v>25</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>139</v>
@@ -15699,10 +15312,10 @@
         <v>140</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>142</v>
@@ -15731,7 +15344,7 @@
         <v>35</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>145</v>
@@ -15760,7 +15373,7 @@
         <v>40</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>148</v>
@@ -15789,7 +15402,7 @@
         <v>45</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>151</v>
@@ -15818,7 +15431,7 @@
         <v>49</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D41" t="s" s="0">
         <v>153</v>
@@ -15850,7 +15463,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -15876,7 +15489,7 @@
         <v>7</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D43" t="s" s="0">
         <v>156</v>

--- a/src/main/java/video/call/data/topics.xlsx
+++ b/src/main/java/video/call/data/topics.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="749">
   <si>
     <t>Part</t>
   </si>
@@ -376,9 +376,6 @@
     <t>4_1</t>
   </si>
   <si>
-    <t>3.2</t>
-  </si>
-  <si>
     <t>So what color is your backpack?</t>
   </si>
   <si>
@@ -443,9 +440,6 @@
   </si>
   <si>
     <t>5_1</t>
-  </si>
-  <si>
-    <t>3.3</t>
   </si>
   <si>
     <t>So what color do you want for your new backpack?</t>
@@ -3199,13 +3193,13 @@
         <v>116</v>
       </c>
       <c r="B31" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s" s="0">
         <v>117</v>
       </c>
-      <c r="C31" t="s" s="0">
+      <c r="D31" t="s" s="0">
         <v>118</v>
-      </c>
-      <c r="D31" t="s" s="0">
-        <v>119</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>7</v>
@@ -3225,16 +3219,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B32" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="C32" t="s" s="0">
         <v>121</v>
       </c>
-      <c r="C32" t="s" s="0">
+      <c r="D32" t="s" s="0">
         <v>122</v>
-      </c>
-      <c r="D32" t="s" s="0">
-        <v>123</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>21</v>
@@ -3254,16 +3248,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C33" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="D33" t="s" s="0">
         <v>125</v>
-      </c>
-      <c r="D33" t="s" s="0">
-        <v>126</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>7</v>
@@ -3283,16 +3277,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="C34" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="B34" t="s" s="0">
-        <v>127</v>
-      </c>
-      <c r="C34" t="s" s="0">
+      <c r="D34" t="s" s="0">
         <v>125</v>
-      </c>
-      <c r="D34" t="s" s="0">
-        <v>126</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>7</v>
@@ -3312,16 +3306,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C35" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="D35" t="s" s="0">
         <v>129</v>
-      </c>
-      <c r="D35" t="s" s="0">
-        <v>130</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>7</v>
@@ -3341,16 +3335,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C36" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="D36" t="s" s="0">
         <v>132</v>
-      </c>
-      <c r="D36" t="s" s="0">
-        <v>133</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -3370,16 +3364,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C37" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="D37" t="s" s="0">
         <v>135</v>
-      </c>
-      <c r="D37" t="s" s="0">
-        <v>136</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -3399,16 +3393,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C38" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="D38" t="s" s="0">
         <v>132</v>
-      </c>
-      <c r="D38" t="s" s="0">
-        <v>133</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -3428,7 +3422,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>52</v>
@@ -3437,7 +3431,7 @@
         <v>7</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -3457,16 +3451,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C40" t="s" s="0">
         <v>139</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="D40" t="s" s="0">
         <v>140</v>
-      </c>
-      <c r="C40" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="D40" t="s" s="0">
-        <v>142</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -3486,16 +3480,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B41" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C41" t="s" s="0">
         <v>121</v>
       </c>
-      <c r="C41" t="s" s="0">
-        <v>122</v>
-      </c>
       <c r="D41" t="s" s="0">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>21</v>
@@ -3515,16 +3509,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -3544,16 +3538,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="D43" t="s" s="0">
         <v>145</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>148</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>147</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -3573,16 +3567,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -3602,16 +3596,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>7</v>
@@ -3631,16 +3625,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>7</v>
@@ -3660,16 +3654,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B47" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>7</v>
@@ -3689,7 +3683,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>52</v>
@@ -3698,7 +3692,7 @@
         <v>7</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>7</v>
@@ -3718,16 +3712,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="D49" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B49" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C49" t="s" s="0">
-        <v>160</v>
-      </c>
-      <c r="D49" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>7</v>
@@ -3792,7 +3786,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -3804,10 +3798,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -3821,7 +3815,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -3836,7 +3830,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -3847,10 +3841,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -3865,7 +3859,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -3879,7 +3873,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -3894,7 +3888,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -3905,10 +3899,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -3923,7 +3917,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -3937,7 +3931,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -3952,7 +3946,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -3966,7 +3960,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -3995,7 +3989,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -4024,7 +4018,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -4082,7 +4076,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -4108,10 +4102,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -4140,7 +4134,7 @@
         <v>24</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -4166,10 +4160,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -4198,7 +4192,7 @@
         <v>34</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>72</v>
@@ -4227,7 +4221,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -4256,7 +4250,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>78</v>
@@ -4285,7 +4279,7 @@
         <v>48</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>75</v>
@@ -4343,7 +4337,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>86</v>
@@ -4352,7 +4346,7 @@
         <v>7</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>7</v>
@@ -4369,10 +4363,10 @@
         <v>87</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>90</v>
@@ -4398,10 +4392,10 @@
         <v>91</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>94</v>
@@ -4430,7 +4424,7 @@
         <v>62</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>97</v>
@@ -4456,10 +4450,10 @@
         <v>98</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>101</v>
@@ -4488,7 +4482,7 @@
         <v>34</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>104</v>
@@ -4497,7 +4491,7 @@
         <v>7</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>7</v>
@@ -4517,7 +4511,7 @@
         <v>39</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>107</v>
@@ -4546,7 +4540,7 @@
         <v>44</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>110</v>
@@ -4575,7 +4569,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>113</v>
@@ -4633,10 +4627,10 @@
         <v>7</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>7</v>
@@ -4656,16 +4650,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>21</v>
@@ -4685,16 +4679,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>21</v>
@@ -4714,16 +4708,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>21</v>
@@ -4743,16 +4737,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>21</v>
@@ -4772,16 +4766,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -4801,16 +4795,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -4830,16 +4824,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -4859,16 +4853,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -4888,16 +4882,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -4917,16 +4911,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -4946,7 +4940,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>52</v>
@@ -4955,7 +4949,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -4975,16 +4969,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>652</v>
+      </c>
+      <c r="D43" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>654</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -5049,7 +5043,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -5061,10 +5055,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -5078,7 +5072,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -5093,7 +5087,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -5104,10 +5098,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -5122,7 +5116,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -5133,10 +5127,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -5151,7 +5145,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -5162,10 +5156,10 @@
         <v>23</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>26</v>
@@ -5180,7 +5174,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -5191,10 +5185,10 @@
         <v>23</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>26</v>
@@ -5209,7 +5203,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -5220,10 +5214,10 @@
         <v>28</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>31</v>
@@ -5238,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>7</v>
@@ -5249,10 +5243,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>26</v>
@@ -5278,7 +5272,7 @@
         <v>34</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>36</v>
@@ -5304,7 +5298,7 @@
         <v>39</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>41</v>
@@ -5333,7 +5327,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>46</v>
@@ -5362,7 +5356,7 @@
         <v>48</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>26</v>
@@ -5414,13 +5408,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>56</v>
@@ -5446,10 +5440,10 @@
         <v>57</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>60</v>
@@ -5475,10 +5469,10 @@
         <v>61</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>64</v>
@@ -5504,10 +5498,10 @@
         <v>66</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>69</v>
@@ -5533,10 +5527,10 @@
         <v>70</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>72</v>
@@ -5562,10 +5556,10 @@
         <v>66</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>69</v>
@@ -5591,10 +5585,10 @@
         <v>73</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>75</v>
@@ -5620,10 +5614,10 @@
         <v>76</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>78</v>
@@ -5652,7 +5646,7 @@
         <v>34</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>81</v>
@@ -5681,7 +5675,7 @@
         <v>39</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>83</v>
@@ -5704,16 +5698,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>7</v>
@@ -5739,7 +5733,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>83</v>
@@ -5762,7 +5756,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>52</v>
@@ -5771,7 +5765,7 @@
         <v>7</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>7</v>
@@ -5797,7 +5791,7 @@
         <v>7</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>86</v>
@@ -5823,10 +5817,10 @@
         <v>87</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>90</v>
@@ -5852,10 +5846,10 @@
         <v>91</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>94</v>
@@ -5884,7 +5878,7 @@
         <v>62</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>97</v>
@@ -5910,10 +5904,10 @@
         <v>98</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>101</v>
@@ -5942,7 +5936,7 @@
         <v>34</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>104</v>
@@ -5971,7 +5965,7 @@
         <v>39</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>107</v>
@@ -6000,7 +5994,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>110</v>
@@ -6029,7 +6023,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>107</v>
@@ -6081,16 +6075,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>699</v>
+      </c>
+      <c r="D38" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B38" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C38" t="s" s="0">
-        <v>701</v>
-      </c>
-      <c r="D38" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -6155,7 +6149,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -6167,10 +6161,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -6184,7 +6178,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -6199,7 +6193,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -6210,10 +6204,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -6222,13 +6216,13 @@
         <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -6242,7 +6236,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -6257,7 +6251,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -6268,10 +6262,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -6286,7 +6280,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -6300,7 +6294,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -6315,7 +6309,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -6329,7 +6323,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -6338,7 +6332,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>7</v>
@@ -6358,7 +6352,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -6387,7 +6381,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -6396,7 +6390,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>7</v>
@@ -6445,7 +6439,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -6471,10 +6465,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -6503,7 +6497,7 @@
         <v>62</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -6532,7 +6526,7 @@
         <v>29</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -6590,7 +6584,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -6619,7 +6613,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>78</v>
@@ -6648,7 +6642,7 @@
         <v>48</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>81</v>
@@ -6706,7 +6700,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>86</v>
@@ -6732,10 +6726,10 @@
         <v>87</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>90</v>
@@ -6764,7 +6758,7 @@
         <v>62</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>94</v>
@@ -6790,10 +6784,10 @@
         <v>95</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>97</v>
@@ -6822,7 +6816,7 @@
         <v>34</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>101</v>
@@ -6851,7 +6845,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>104</v>
@@ -6880,7 +6874,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>107</v>
@@ -6909,7 +6903,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>110</v>
@@ -6967,16 +6961,16 @@
         <v>7</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>7</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>7</v>
@@ -6990,16 +6984,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>21</v>
@@ -7019,16 +7013,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>21</v>
@@ -7048,16 +7042,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>21</v>
@@ -7077,16 +7071,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>7</v>
@@ -7106,16 +7100,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>7</v>
@@ -7135,16 +7129,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -7164,16 +7158,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -7193,16 +7187,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -7222,16 +7216,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -7251,7 +7245,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>52</v>
@@ -7260,7 +7254,7 @@
         <v>7</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -7280,16 +7274,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>748</v>
+      </c>
+      <c r="D41" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C41" t="s" s="0">
-        <v>750</v>
-      </c>
-      <c r="D41" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -7354,7 +7348,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -7363,10 +7357,10 @@
         <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>7</v>
@@ -7383,7 +7377,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -7398,7 +7392,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -7409,10 +7403,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -7421,13 +7415,13 @@
         <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -7441,7 +7435,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -7450,13 +7444,13 @@
         <v>7</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -7467,10 +7461,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -7485,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -7499,7 +7493,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -7514,7 +7508,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -7528,7 +7522,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -7543,7 +7537,7 @@
         <v>7</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>7</v>
@@ -7557,7 +7551,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -7586,7 +7580,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -7644,7 +7638,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -7670,10 +7664,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -7699,10 +7693,10 @@
         <v>61</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -7728,10 +7722,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -7760,7 +7754,7 @@
         <v>62</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>72</v>
@@ -7786,10 +7780,10 @@
         <v>73</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -7815,7 +7809,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>78</v>
@@ -7841,7 +7835,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>81</v>
@@ -7867,7 +7861,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>83</v>
@@ -7876,7 +7870,7 @@
         <v>7</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>7</v>
@@ -7890,16 +7884,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>7</v>
@@ -7916,7 +7910,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -7925,7 +7919,7 @@
         <v>7</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>7</v>
@@ -7948,7 +7942,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -7971,10 +7965,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -7997,10 +7991,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -8026,7 +8020,7 @@
         <v>62</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -8052,10 +8046,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -8064,7 +8058,7 @@
         <v>7</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>7</v>
@@ -8084,7 +8078,7 @@
         <v>34</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -8113,7 +8107,7 @@
         <v>39</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -8142,7 +8136,7 @@
         <v>44</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -8171,7 +8165,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>107</v>
@@ -8229,10 +8223,10 @@
         <v>7</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>7</v>
@@ -8252,16 +8246,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>21</v>
@@ -8281,16 +8275,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>21</v>
@@ -8310,16 +8304,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -8339,16 +8333,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -8368,16 +8362,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -8397,16 +8391,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -8426,16 +8420,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -8455,16 +8449,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -8484,7 +8478,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>52</v>
@@ -8493,7 +8487,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -8513,13 +8507,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="D43" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>230</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -8701,7 +8695,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -8727,7 +8721,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -8750,10 +8744,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -8776,10 +8770,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -8805,7 +8799,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -8828,10 +8822,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -8857,7 +8851,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -8883,7 +8877,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -8909,7 +8903,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -8935,7 +8929,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -8955,7 +8949,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -8964,7 +8958,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -8987,7 +8981,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -8996,10 +8990,10 @@
         <v>7</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>7</v>
@@ -9010,10 +9004,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -9036,10 +9030,10 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>64</v>
@@ -9065,7 +9059,7 @@
         <v>62</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -9074,7 +9068,7 @@
         <v>7</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>7</v>
@@ -9088,10 +9082,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -9117,7 +9111,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -9143,7 +9137,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -9169,7 +9163,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -9195,7 +9189,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>78</v>
@@ -9215,7 +9209,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -9247,7 +9241,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -9270,10 +9264,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -9296,10 +9290,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -9325,7 +9319,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -9348,10 +9342,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -9377,7 +9371,7 @@
         <v>34</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -9403,7 +9397,7 @@
         <v>39</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -9429,7 +9423,7 @@
         <v>44</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -9455,7 +9449,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>107</v>
@@ -9507,10 +9501,10 @@
         <v>7</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>7</v>
@@ -9527,16 +9521,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>21</v>
@@ -9553,16 +9547,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>21</v>
@@ -9579,16 +9573,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>21</v>
@@ -9605,16 +9599,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -9631,16 +9625,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -9657,16 +9651,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -9683,16 +9677,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -9709,16 +9703,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -9735,16 +9729,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -9761,7 +9755,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>52</v>
@@ -9770,7 +9764,7 @@
         <v>7</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -9787,16 +9781,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="D44" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s" s="0">
-        <v>282</v>
-      </c>
-      <c r="D44" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -9988,7 +9982,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -10003,7 +9997,7 @@
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -10026,13 +10020,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -10043,10 +10037,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -10061,7 +10055,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -10072,10 +10066,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -10090,7 +10084,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -10101,10 +10095,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -10119,7 +10113,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -10133,7 +10127,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -10148,7 +10142,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -10162,7 +10156,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -10191,7 +10185,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -10217,7 +10211,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -10246,7 +10240,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -10269,7 +10263,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -10278,7 +10272,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -10304,7 +10298,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -10330,10 +10324,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -10359,10 +10353,10 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>64</v>
@@ -10388,10 +10382,10 @@
         <v>66</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -10417,10 +10411,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -10449,7 +10443,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -10478,7 +10472,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -10507,7 +10501,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -10536,7 +10530,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>83</v>
@@ -10559,7 +10553,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -10568,7 +10562,7 @@
         <v>7</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>7</v>
@@ -10594,7 +10588,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -10620,10 +10614,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -10649,10 +10643,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -10678,10 +10672,10 @@
         <v>95</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -10707,10 +10701,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -10736,10 +10730,10 @@
         <v>102</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -10768,7 +10762,7 @@
         <v>34</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -10797,7 +10791,7 @@
         <v>39</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -10826,7 +10820,7 @@
         <v>44</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>113</v>
@@ -10855,7 +10849,7 @@
         <v>48</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>115</v>
@@ -10878,7 +10872,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>52</v>
@@ -10887,7 +10881,7 @@
         <v>7</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>7</v>
@@ -10913,10 +10907,10 @@
         <v>7</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>7</v>
@@ -10936,16 +10930,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>21</v>
@@ -10965,16 +10959,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>21</v>
@@ -10994,16 +10988,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -11023,16 +11017,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -11052,16 +11046,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -11081,16 +11075,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -11110,16 +11104,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -11139,16 +11133,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -11168,7 +11162,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>52</v>
@@ -11177,7 +11171,7 @@
         <v>7</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -11197,16 +11191,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>334</v>
+      </c>
+      <c r="D44" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s" s="0">
-        <v>336</v>
-      </c>
-      <c r="D44" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -11291,7 +11285,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -11303,10 +11297,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -11320,7 +11314,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -11329,13 +11323,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -11346,10 +11340,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -11364,7 +11358,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -11375,10 +11369,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -11393,7 +11387,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -11407,7 +11401,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -11422,7 +11416,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -11433,10 +11427,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -11451,7 +11445,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -11465,7 +11459,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -11494,7 +11488,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -11523,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -11552,7 +11546,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -11575,7 +11569,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -11584,7 +11578,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -11610,7 +11604,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -11619,7 +11613,7 @@
         <v>7</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>7</v>
@@ -11636,10 +11630,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -11665,10 +11659,10 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>64</v>
@@ -11697,7 +11691,7 @@
         <v>62</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -11723,10 +11717,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -11755,7 +11749,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -11784,7 +11778,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -11813,7 +11807,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -11842,7 +11836,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>78</v>
@@ -11900,7 +11894,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -11926,10 +11920,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -11955,10 +11949,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -11987,7 +11981,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -12013,10 +12007,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -12045,7 +12039,7 @@
         <v>34</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -12074,7 +12068,7 @@
         <v>39</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -12103,7 +12097,7 @@
         <v>44</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -12132,7 +12126,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>113</v>
@@ -12190,10 +12184,10 @@
         <v>7</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>7</v>
@@ -12213,16 +12207,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>21</v>
@@ -12242,16 +12236,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>21</v>
@@ -12271,16 +12265,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>21</v>
@@ -12300,16 +12294,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -12329,16 +12323,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -12358,16 +12352,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -12387,16 +12381,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -12416,16 +12410,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -12445,16 +12439,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -12474,7 +12468,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>52</v>
@@ -12483,7 +12477,7 @@
         <v>7</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -12503,16 +12497,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="D44" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s" s="0">
-        <v>395</v>
-      </c>
-      <c r="D44" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -12542,7 +12536,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>1</v>
@@ -12577,7 +12571,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -12592,7 +12586,7 @@
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -12606,7 +12600,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -12621,7 +12615,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -12632,10 +12626,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -12650,7 +12644,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -12661,10 +12655,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -12679,7 +12673,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -12693,7 +12687,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -12708,7 +12702,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -12719,10 +12713,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -12737,7 +12731,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -12751,7 +12745,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -12780,7 +12774,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -12809,7 +12803,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -12838,7 +12832,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -12861,7 +12855,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -12870,7 +12864,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -12896,7 +12890,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -12922,10 +12916,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -12951,7 +12945,7 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>93</v>
@@ -12983,7 +12977,7 @@
         <v>62</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -13009,10 +13003,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -13041,7 +13035,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -13070,7 +13064,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -13099,7 +13093,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -13128,7 +13122,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>78</v>
@@ -13151,7 +13145,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -13186,7 +13180,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -13212,10 +13206,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -13241,10 +13235,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>113</v>
@@ -13270,10 +13264,10 @@
         <v>95</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>94</v>
@@ -13299,10 +13293,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>97</v>
@@ -13331,7 +13325,7 @@
         <v>24</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>101</v>
@@ -13357,10 +13351,10 @@
         <v>105</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>104</v>
@@ -13389,7 +13383,7 @@
         <v>34</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>107</v>
@@ -13418,7 +13412,7 @@
         <v>39</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>110</v>
@@ -13447,7 +13441,7 @@
         <v>44</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>113</v>
@@ -13470,13 +13464,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>115</v>
@@ -13499,7 +13493,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>52</v>
@@ -13508,7 +13502,7 @@
         <v>7</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>7</v>
@@ -13534,10 +13528,10 @@
         <v>7</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>7</v>
@@ -13557,16 +13551,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>21</v>
@@ -13586,16 +13580,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>21</v>
@@ -13615,16 +13609,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -13644,16 +13638,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -13673,16 +13667,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -13702,16 +13696,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -13731,16 +13725,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -13760,16 +13754,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -13789,7 +13783,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>52</v>
@@ -13798,7 +13792,7 @@
         <v>7</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -13818,16 +13812,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>450</v>
+      </c>
+      <c r="D45" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B45" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C45" t="s" s="0">
-        <v>452</v>
-      </c>
-      <c r="D45" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>7</v>
@@ -13892,7 +13886,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -13907,7 +13901,7 @@
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -13921,7 +13915,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -13936,7 +13930,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -13947,10 +13941,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -13965,7 +13959,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -13979,7 +13973,7 @@
         <v>62</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -13994,7 +13988,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -14005,10 +13999,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -14017,13 +14011,13 @@
         <v>7</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -14037,7 +14031,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -14052,7 +14046,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -14066,7 +14060,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -14095,7 +14089,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -14124,7 +14118,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -14182,7 +14176,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -14202,10 +14196,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -14225,10 +14219,10 @@
         <v>61</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -14248,10 +14242,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -14271,10 +14265,10 @@
         <v>70</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>72</v>
@@ -14297,7 +14291,7 @@
         <v>34</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -14320,7 +14314,7 @@
         <v>39</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>78</v>
@@ -14343,7 +14337,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>81</v>
@@ -14366,10 +14360,10 @@
         <v>48</v>
       </c>
       <c r="C20" t="s" s="0">
+        <v>477</v>
+      </c>
+      <c r="D20" t="s" s="0">
         <v>479</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>481</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>7</v>
@@ -14412,7 +14406,7 @@
         <v>7</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>86</v>
@@ -14421,7 +14415,7 @@
         <v>7</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>7</v>
@@ -14438,10 +14432,10 @@
         <v>87</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>90</v>
@@ -14467,10 +14461,10 @@
         <v>91</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>94</v>
@@ -14499,7 +14493,7 @@
         <v>24</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>97</v>
@@ -14525,10 +14519,10 @@
         <v>98</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>101</v>
@@ -14557,7 +14551,7 @@
         <v>34</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>104</v>
@@ -14586,7 +14580,7 @@
         <v>39</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>107</v>
@@ -14615,7 +14609,7 @@
         <v>44</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>110</v>
@@ -14644,7 +14638,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>113</v>
@@ -14702,10 +14696,10 @@
         <v>7</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>7</v>
@@ -14725,16 +14719,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>21</v>
@@ -14754,16 +14748,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>21</v>
@@ -14783,16 +14777,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>21</v>
@@ -14812,16 +14806,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -14841,16 +14835,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -14870,16 +14864,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -14899,16 +14893,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -14928,16 +14922,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -14957,16 +14951,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -14986,7 +14980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>52</v>
@@ -14995,7 +14989,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -15015,13 +15009,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>505</v>
+      </c>
+      <c r="D43" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>507</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -15097,7 +15091,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -15117,7 +15111,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -15134,10 +15128,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -15157,7 +15151,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -15174,10 +15168,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -15197,7 +15191,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -15217,7 +15211,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -15237,7 +15231,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -15257,7 +15251,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -15297,7 +15291,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -15314,10 +15308,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -15337,7 +15331,7 @@
         <v>62</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -15354,10 +15348,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -15377,7 +15371,7 @@
         <v>34</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>72</v>
@@ -15397,7 +15391,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -15437,7 +15431,7 @@
         <v>48</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>81</v>
@@ -15474,10 +15468,10 @@
         <v>84</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>86</v>
@@ -15494,10 +15488,10 @@
         <v>87</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>90</v>
@@ -15514,10 +15508,10 @@
         <v>91</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>94</v>
@@ -15537,7 +15531,7 @@
         <v>62</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>97</v>
@@ -15554,10 +15548,10 @@
         <v>98</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>101</v>
@@ -15577,7 +15571,7 @@
         <v>34</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>104</v>
@@ -15597,7 +15591,7 @@
         <v>39</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>107</v>
@@ -15617,7 +15611,7 @@
         <v>44</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>110</v>
@@ -15637,7 +15631,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -15677,10 +15671,10 @@
         <v>7</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>7</v>
@@ -15691,16 +15685,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>21</v>
@@ -15711,16 +15705,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>21</v>
@@ -15731,16 +15725,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>7</v>
@@ -15751,16 +15745,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>7</v>
@@ -15771,16 +15765,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -15791,16 +15785,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -15811,16 +15805,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -15831,16 +15825,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -15851,7 +15845,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>52</v>
@@ -15860,7 +15854,7 @@
         <v>7</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -15871,16 +15865,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>547</v>
+      </c>
+      <c r="D41" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C41" t="s" s="0">
-        <v>549</v>
-      </c>
-      <c r="D41" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -15936,7 +15930,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -15945,13 +15939,13 @@
         <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -15965,7 +15959,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -15977,10 +15971,10 @@
         <v>7</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -15991,10 +15985,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -16009,7 +16003,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -16020,10 +16014,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -16038,7 +16032,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -16052,7 +16046,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -16067,7 +16061,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -16078,10 +16072,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -16096,7 +16090,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -16110,7 +16104,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -16136,7 +16130,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -16165,7 +16159,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -16194,7 +16188,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -16217,7 +16211,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -16226,7 +16220,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -16252,7 +16246,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -16278,10 +16272,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -16307,10 +16301,10 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>64</v>
@@ -16339,7 +16333,7 @@
         <v>24</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -16365,10 +16359,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -16397,7 +16391,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -16426,7 +16420,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -16455,7 +16449,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -16484,7 +16478,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>83</v>
@@ -16507,7 +16501,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -16516,7 +16510,7 @@
         <v>7</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>7</v>
@@ -16542,7 +16536,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -16568,10 +16562,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -16597,10 +16591,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -16626,10 +16620,10 @@
         <v>95</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -16658,7 +16652,7 @@
         <v>24</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -16684,10 +16678,10 @@
         <v>102</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -16716,7 +16710,7 @@
         <v>34</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -16745,7 +16739,7 @@
         <v>39</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -16774,7 +16768,7 @@
         <v>44</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>113</v>
@@ -16803,7 +16797,7 @@
         <v>48</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>115</v>
@@ -16826,7 +16820,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>52</v>
@@ -16835,7 +16829,7 @@
         <v>7</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>7</v>
@@ -16861,10 +16855,10 @@
         <v>7</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>7</v>
@@ -16884,16 +16878,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>21</v>
@@ -16913,16 +16907,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>7</v>
@@ -16942,16 +16936,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -16971,16 +16965,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -17000,16 +16994,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -17029,16 +17023,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -17058,16 +17052,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -17087,7 +17081,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>52</v>
@@ -17096,7 +17090,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -17116,16 +17110,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>599</v>
+      </c>
+      <c r="D43" t="s" s="0">
         <v>159</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>601</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>161</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>

--- a/src/main/java/video/call/data/topics.xlsx
+++ b/src/main/java/video/call/data/topics.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="750">
   <si>
     <t>Part</t>
   </si>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t>5_1</t>
+  </si>
+  <si>
+    <t>else</t>
   </si>
   <si>
     <t>So what color do you want for your new backpack?</t>
@@ -3454,13 +3457,13 @@
         <v>138</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -3480,7 +3483,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>120</v>
@@ -3489,7 +3492,7 @@
         <v>121</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>21</v>
@@ -3509,16 +3512,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>24</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -3538,16 +3541,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="D43" t="s" s="0">
         <v>146</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>144</v>
-      </c>
-      <c r="D43" t="s" s="0">
-        <v>145</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -3567,16 +3570,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -3596,7 +3599,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>39</v>
@@ -3605,7 +3608,7 @@
         <v>131</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>7</v>
@@ -3625,16 +3628,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>7</v>
@@ -3654,7 +3657,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B47" t="s" s="0">
         <v>48</v>
@@ -3663,7 +3666,7 @@
         <v>131</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>7</v>
@@ -3683,7 +3686,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>52</v>
@@ -3692,7 +3695,7 @@
         <v>7</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>7</v>
@@ -3712,16 +3715,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B49" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>7</v>
@@ -3786,7 +3789,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -3798,10 +3801,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -3815,7 +3818,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -3830,7 +3833,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -3841,10 +3844,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -3859,7 +3862,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -3873,7 +3876,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -3888,7 +3891,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -3899,10 +3902,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -3917,7 +3920,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -3931,7 +3934,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -3946,7 +3949,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -3960,7 +3963,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -3989,7 +3992,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -4018,7 +4021,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -4076,7 +4079,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -4102,10 +4105,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -4134,7 +4137,7 @@
         <v>24</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -4160,10 +4163,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -4192,7 +4195,7 @@
         <v>34</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>72</v>
@@ -4221,7 +4224,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -4250,7 +4253,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>78</v>
@@ -4279,7 +4282,7 @@
         <v>48</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>75</v>
@@ -4337,7 +4340,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>86</v>
@@ -4346,7 +4349,7 @@
         <v>7</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>7</v>
@@ -4363,10 +4366,10 @@
         <v>87</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>90</v>
@@ -4392,10 +4395,10 @@
         <v>91</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>94</v>
@@ -4424,7 +4427,7 @@
         <v>62</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>97</v>
@@ -4450,10 +4453,10 @@
         <v>98</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>101</v>
@@ -4482,7 +4485,7 @@
         <v>34</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>104</v>
@@ -4491,7 +4494,7 @@
         <v>7</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>7</v>
@@ -4511,7 +4514,7 @@
         <v>39</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>107</v>
@@ -4540,7 +4543,7 @@
         <v>44</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>110</v>
@@ -4569,7 +4572,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>113</v>
@@ -4627,7 +4630,7 @@
         <v>7</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>118</v>
@@ -4653,10 +4656,10 @@
         <v>119</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>122</v>
@@ -4682,10 +4685,10 @@
         <v>123</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>125</v>
@@ -4711,10 +4714,10 @@
         <v>127</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>129</v>
@@ -4740,10 +4743,10 @@
         <v>127</v>
       </c>
       <c r="B35" t="s" s="0">
+        <v>646</v>
+      </c>
+      <c r="C35" t="s" s="0">
         <v>645</v>
-      </c>
-      <c r="C35" t="s" s="0">
-        <v>644</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>129</v>
@@ -4772,7 +4775,7 @@
         <v>24</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>132</v>
@@ -4798,10 +4801,10 @@
         <v>133</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>135</v>
@@ -4830,7 +4833,7 @@
         <v>34</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>137</v>
@@ -4853,16 +4856,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -4882,16 +4885,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -4911,16 +4914,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -4940,7 +4943,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>52</v>
@@ -4949,7 +4952,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -4969,16 +4972,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -5043,7 +5046,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -5055,10 +5058,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -5072,7 +5075,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -5087,7 +5090,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -5098,10 +5101,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -5116,7 +5119,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -5127,10 +5130,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -5145,7 +5148,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -5156,10 +5159,10 @@
         <v>23</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>26</v>
@@ -5174,7 +5177,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -5185,10 +5188,10 @@
         <v>23</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>26</v>
@@ -5203,7 +5206,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -5214,10 +5217,10 @@
         <v>28</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>31</v>
@@ -5232,7 +5235,7 @@
         <v>7</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>7</v>
@@ -5243,10 +5246,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>26</v>
@@ -5272,7 +5275,7 @@
         <v>34</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>36</v>
@@ -5298,7 +5301,7 @@
         <v>39</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>41</v>
@@ -5327,7 +5330,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>46</v>
@@ -5356,7 +5359,7 @@
         <v>48</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>26</v>
@@ -5408,13 +5411,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>56</v>
@@ -5440,10 +5443,10 @@
         <v>57</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>60</v>
@@ -5469,10 +5472,10 @@
         <v>61</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>64</v>
@@ -5498,10 +5501,10 @@
         <v>66</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>69</v>
@@ -5527,10 +5530,10 @@
         <v>70</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>72</v>
@@ -5556,10 +5559,10 @@
         <v>66</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>69</v>
@@ -5585,10 +5588,10 @@
         <v>73</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>75</v>
@@ -5614,10 +5617,10 @@
         <v>76</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>78</v>
@@ -5646,7 +5649,7 @@
         <v>34</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>81</v>
@@ -5675,7 +5678,7 @@
         <v>39</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>83</v>
@@ -5698,16 +5701,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>7</v>
@@ -5733,7 +5736,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>83</v>
@@ -5756,7 +5759,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>52</v>
@@ -5765,7 +5768,7 @@
         <v>7</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>7</v>
@@ -5791,7 +5794,7 @@
         <v>7</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>86</v>
@@ -5817,10 +5820,10 @@
         <v>87</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>90</v>
@@ -5846,10 +5849,10 @@
         <v>91</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>94</v>
@@ -5878,7 +5881,7 @@
         <v>62</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>97</v>
@@ -5904,10 +5907,10 @@
         <v>98</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>101</v>
@@ -5936,7 +5939,7 @@
         <v>34</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>104</v>
@@ -5965,7 +5968,7 @@
         <v>39</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>107</v>
@@ -5994,7 +5997,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>110</v>
@@ -6023,7 +6026,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>107</v>
@@ -6075,16 +6078,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -6149,7 +6152,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -6161,10 +6164,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -6178,7 +6181,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -6193,7 +6196,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -6204,10 +6207,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -6216,13 +6219,13 @@
         <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -6236,7 +6239,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -6251,7 +6254,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -6262,10 +6265,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -6280,7 +6283,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -6294,7 +6297,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -6309,7 +6312,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -6323,7 +6326,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -6332,7 +6335,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>7</v>
@@ -6352,7 +6355,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -6381,7 +6384,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -6390,7 +6393,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>7</v>
@@ -6439,7 +6442,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -6465,10 +6468,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -6497,7 +6500,7 @@
         <v>62</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -6526,7 +6529,7 @@
         <v>29</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -6584,7 +6587,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -6613,7 +6616,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>78</v>
@@ -6642,7 +6645,7 @@
         <v>48</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>81</v>
@@ -6700,7 +6703,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>86</v>
@@ -6726,10 +6729,10 @@
         <v>87</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>90</v>
@@ -6758,7 +6761,7 @@
         <v>62</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>94</v>
@@ -6784,10 +6787,10 @@
         <v>95</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>97</v>
@@ -6816,7 +6819,7 @@
         <v>34</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>101</v>
@@ -6845,7 +6848,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>104</v>
@@ -6874,7 +6877,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>107</v>
@@ -6903,7 +6906,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>110</v>
@@ -6961,7 +6964,7 @@
         <v>7</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>118</v>
@@ -6970,7 +6973,7 @@
         <v>7</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>7</v>
@@ -6987,10 +6990,10 @@
         <v>119</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>122</v>
@@ -7016,10 +7019,10 @@
         <v>123</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>125</v>
@@ -7045,10 +7048,10 @@
         <v>127</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>129</v>
@@ -7077,7 +7080,7 @@
         <v>24</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>132</v>
@@ -7103,10 +7106,10 @@
         <v>133</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>135</v>
@@ -7135,7 +7138,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>137</v>
@@ -7158,16 +7161,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>7</v>
@@ -7187,16 +7190,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -7216,16 +7219,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -7245,7 +7248,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>52</v>
@@ -7254,7 +7257,7 @@
         <v>7</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -7274,16 +7277,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -7348,7 +7351,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -7357,10 +7360,10 @@
         <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>7</v>
@@ -7377,7 +7380,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -7392,7 +7395,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -7403,10 +7406,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -7415,13 +7418,13 @@
         <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -7435,7 +7438,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -7444,13 +7447,13 @@
         <v>7</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -7461,10 +7464,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -7479,7 +7482,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -7493,7 +7496,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -7508,7 +7511,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -7522,7 +7525,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -7537,7 +7540,7 @@
         <v>7</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>7</v>
@@ -7551,7 +7554,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -7580,7 +7583,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -7638,7 +7641,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -7664,10 +7667,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -7693,10 +7696,10 @@
         <v>61</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -7722,10 +7725,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -7754,7 +7757,7 @@
         <v>62</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>72</v>
@@ -7780,10 +7783,10 @@
         <v>73</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -7809,7 +7812,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>78</v>
@@ -7835,7 +7838,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>81</v>
@@ -7861,7 +7864,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>83</v>
@@ -7870,7 +7873,7 @@
         <v>7</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>7</v>
@@ -7884,16 +7887,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>7</v>
@@ -7910,7 +7913,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -7919,7 +7922,7 @@
         <v>7</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>7</v>
@@ -7942,7 +7945,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -7965,10 +7968,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -7991,10 +7994,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -8020,7 +8023,7 @@
         <v>62</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -8046,10 +8049,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -8058,7 +8061,7 @@
         <v>7</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>7</v>
@@ -8078,7 +8081,7 @@
         <v>34</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -8107,7 +8110,7 @@
         <v>39</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -8136,7 +8139,7 @@
         <v>44</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -8165,7 +8168,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>107</v>
@@ -8223,7 +8226,7 @@
         <v>7</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>118</v>
@@ -8249,10 +8252,10 @@
         <v>119</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>122</v>
@@ -8278,10 +8281,10 @@
         <v>123</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>125</v>
@@ -8310,7 +8313,7 @@
         <v>24</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>129</v>
@@ -8336,10 +8339,10 @@
         <v>130</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>132</v>
@@ -8368,7 +8371,7 @@
         <v>34</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>135</v>
@@ -8397,7 +8400,7 @@
         <v>39</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>137</v>
@@ -8420,16 +8423,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -8449,16 +8452,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -8478,7 +8481,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>52</v>
@@ -8487,7 +8490,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -8507,13 +8510,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -8695,7 +8698,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -8721,7 +8724,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -8744,10 +8747,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -8770,10 +8773,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -8799,7 +8802,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -8822,10 +8825,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -8851,7 +8854,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -8877,7 +8880,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -8903,7 +8906,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -8929,7 +8932,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -8949,7 +8952,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -8958,7 +8961,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -8981,7 +8984,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -8990,10 +8993,10 @@
         <v>7</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>7</v>
@@ -9004,10 +9007,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -9030,10 +9033,10 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>64</v>
@@ -9059,7 +9062,7 @@
         <v>62</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -9068,7 +9071,7 @@
         <v>7</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>7</v>
@@ -9082,10 +9085,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -9111,7 +9114,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -9137,7 +9140,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -9163,7 +9166,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -9189,7 +9192,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>78</v>
@@ -9209,7 +9212,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -9241,7 +9244,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -9264,10 +9267,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -9290,10 +9293,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -9319,7 +9322,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -9342,10 +9345,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -9371,7 +9374,7 @@
         <v>34</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -9397,7 +9400,7 @@
         <v>39</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -9423,7 +9426,7 @@
         <v>44</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -9449,7 +9452,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>107</v>
@@ -9501,7 +9504,7 @@
         <v>7</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>118</v>
@@ -9524,10 +9527,10 @@
         <v>119</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>122</v>
@@ -9550,10 +9553,10 @@
         <v>123</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>125</v>
@@ -9576,13 +9579,13 @@
         <v>127</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>21</v>
@@ -9605,7 +9608,7 @@
         <v>24</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>129</v>
@@ -9628,10 +9631,10 @@
         <v>133</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>132</v>
@@ -9657,7 +9660,7 @@
         <v>34</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>135</v>
@@ -9677,13 +9680,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>137</v>
@@ -9703,16 +9706,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -9729,13 +9732,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D42" t="s" s="0">
         <v>137</v>
@@ -9755,7 +9758,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>52</v>
@@ -9764,7 +9767,7 @@
         <v>7</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -9781,16 +9784,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -9982,7 +9985,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -9997,7 +10000,7 @@
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -10020,13 +10023,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -10037,10 +10040,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -10055,7 +10058,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -10066,10 +10069,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -10084,7 +10087,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -10095,10 +10098,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -10113,7 +10116,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -10127,7 +10130,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -10142,7 +10145,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -10156,7 +10159,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -10185,7 +10188,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -10211,7 +10214,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -10240,7 +10243,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -10263,7 +10266,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -10272,7 +10275,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -10298,7 +10301,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -10324,10 +10327,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -10353,10 +10356,10 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>64</v>
@@ -10382,10 +10385,10 @@
         <v>66</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -10411,10 +10414,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -10443,7 +10446,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -10472,7 +10475,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -10501,7 +10504,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -10530,7 +10533,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>83</v>
@@ -10553,7 +10556,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -10562,7 +10565,7 @@
         <v>7</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>7</v>
@@ -10588,7 +10591,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -10614,10 +10617,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -10643,10 +10646,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -10672,10 +10675,10 @@
         <v>95</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -10701,10 +10704,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -10730,10 +10733,10 @@
         <v>102</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -10762,7 +10765,7 @@
         <v>34</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -10791,7 +10794,7 @@
         <v>39</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -10820,7 +10823,7 @@
         <v>44</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>113</v>
@@ -10849,7 +10852,7 @@
         <v>48</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>115</v>
@@ -10872,7 +10875,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>52</v>
@@ -10881,7 +10884,7 @@
         <v>7</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>7</v>
@@ -10907,7 +10910,7 @@
         <v>7</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>118</v>
@@ -10933,10 +10936,10 @@
         <v>119</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>122</v>
@@ -10962,10 +10965,10 @@
         <v>123</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>125</v>
@@ -10994,7 +10997,7 @@
         <v>24</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>129</v>
@@ -11020,10 +11023,10 @@
         <v>130</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>132</v>
@@ -11052,7 +11055,7 @@
         <v>34</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>135</v>
@@ -11081,7 +11084,7 @@
         <v>39</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>137</v>
@@ -11104,16 +11107,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -11133,16 +11136,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -11162,7 +11165,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>52</v>
@@ -11171,7 +11174,7 @@
         <v>7</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -11191,16 +11194,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -11285,7 +11288,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -11297,10 +11300,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -11314,7 +11317,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -11323,13 +11326,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -11340,10 +11343,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -11358,7 +11361,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -11369,10 +11372,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -11387,7 +11390,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -11401,7 +11404,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -11416,7 +11419,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -11427,10 +11430,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -11445,7 +11448,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -11459,7 +11462,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -11488,7 +11491,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -11517,7 +11520,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -11546,7 +11549,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -11569,7 +11572,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -11578,7 +11581,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -11604,7 +11607,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -11613,7 +11616,7 @@
         <v>7</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>7</v>
@@ -11630,10 +11633,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -11659,10 +11662,10 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>64</v>
@@ -11691,7 +11694,7 @@
         <v>62</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -11717,10 +11720,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -11749,7 +11752,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -11778,7 +11781,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -11807,7 +11810,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -11836,7 +11839,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>78</v>
@@ -11894,7 +11897,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -11920,10 +11923,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -11949,10 +11952,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -11981,7 +11984,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -12007,10 +12010,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -12039,7 +12042,7 @@
         <v>34</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -12068,7 +12071,7 @@
         <v>39</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -12097,7 +12100,7 @@
         <v>44</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -12126,7 +12129,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>113</v>
@@ -12184,7 +12187,7 @@
         <v>7</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>118</v>
@@ -12210,10 +12213,10 @@
         <v>119</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>122</v>
@@ -12239,10 +12242,10 @@
         <v>123</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>125</v>
@@ -12268,10 +12271,10 @@
         <v>127</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>129</v>
@@ -12300,7 +12303,7 @@
         <v>24</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>132</v>
@@ -12326,10 +12329,10 @@
         <v>133</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>135</v>
@@ -12358,7 +12361,7 @@
         <v>34</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>137</v>
@@ -12381,16 +12384,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -12410,16 +12413,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -12439,16 +12442,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -12468,7 +12471,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>52</v>
@@ -12477,7 +12480,7 @@
         <v>7</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -12497,16 +12500,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -12536,7 +12539,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>1</v>
@@ -12571,7 +12574,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -12586,7 +12589,7 @@
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -12600,7 +12603,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -12615,7 +12618,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -12626,10 +12629,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -12644,7 +12647,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -12655,10 +12658,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -12673,7 +12676,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -12687,7 +12690,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -12702,7 +12705,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -12713,10 +12716,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -12731,7 +12734,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -12745,7 +12748,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -12774,7 +12777,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -12803,7 +12806,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -12832,7 +12835,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -12855,7 +12858,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -12864,7 +12867,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -12890,7 +12893,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -12916,10 +12919,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -12945,7 +12948,7 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>93</v>
@@ -12977,7 +12980,7 @@
         <v>62</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -13003,10 +13006,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -13035,7 +13038,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -13064,7 +13067,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -13093,7 +13096,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -13122,7 +13125,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>78</v>
@@ -13145,7 +13148,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -13180,7 +13183,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -13206,10 +13209,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -13235,10 +13238,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>113</v>
@@ -13264,10 +13267,10 @@
         <v>95</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>94</v>
@@ -13293,10 +13296,10 @@
         <v>98</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>97</v>
@@ -13325,7 +13328,7 @@
         <v>24</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>101</v>
@@ -13351,10 +13354,10 @@
         <v>105</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>104</v>
@@ -13383,7 +13386,7 @@
         <v>34</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>107</v>
@@ -13412,7 +13415,7 @@
         <v>39</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>110</v>
@@ -13441,7 +13444,7 @@
         <v>44</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>113</v>
@@ -13464,13 +13467,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>115</v>
@@ -13493,7 +13496,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>52</v>
@@ -13502,7 +13505,7 @@
         <v>7</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>7</v>
@@ -13528,7 +13531,7 @@
         <v>7</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>118</v>
@@ -13554,10 +13557,10 @@
         <v>119</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>122</v>
@@ -13583,10 +13586,10 @@
         <v>123</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>125</v>
@@ -13615,7 +13618,7 @@
         <v>24</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>129</v>
@@ -13641,10 +13644,10 @@
         <v>130</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>132</v>
@@ -13673,7 +13676,7 @@
         <v>34</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>135</v>
@@ -13702,7 +13705,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D41" t="s" s="0">
         <v>137</v>
@@ -13725,16 +13728,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -13754,16 +13757,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -13783,7 +13786,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>52</v>
@@ -13792,7 +13795,7 @@
         <v>7</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>7</v>
@@ -13812,16 +13815,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>7</v>
@@ -13886,7 +13889,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -13901,7 +13904,7 @@
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -13915,7 +13918,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -13930,7 +13933,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -13941,10 +13944,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -13959,7 +13962,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -13973,7 +13976,7 @@
         <v>62</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -13988,7 +13991,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -13999,10 +14002,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -14011,13 +14014,13 @@
         <v>7</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -14031,7 +14034,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -14046,7 +14049,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -14060,7 +14063,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -14089,7 +14092,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -14118,7 +14121,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -14176,7 +14179,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -14196,10 +14199,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -14219,10 +14222,10 @@
         <v>61</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -14242,10 +14245,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -14265,10 +14268,10 @@
         <v>70</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>72</v>
@@ -14291,7 +14294,7 @@
         <v>34</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -14314,7 +14317,7 @@
         <v>39</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>78</v>
@@ -14337,7 +14340,7 @@
         <v>44</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>81</v>
@@ -14360,10 +14363,10 @@
         <v>48</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>7</v>
@@ -14406,7 +14409,7 @@
         <v>7</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>86</v>
@@ -14415,7 +14418,7 @@
         <v>7</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>7</v>
@@ -14432,10 +14435,10 @@
         <v>87</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>90</v>
@@ -14461,10 +14464,10 @@
         <v>91</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>94</v>
@@ -14493,7 +14496,7 @@
         <v>24</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>97</v>
@@ -14519,10 +14522,10 @@
         <v>98</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>101</v>
@@ -14551,7 +14554,7 @@
         <v>34</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>104</v>
@@ -14580,7 +14583,7 @@
         <v>39</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>107</v>
@@ -14609,7 +14612,7 @@
         <v>44</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>110</v>
@@ -14638,7 +14641,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>113</v>
@@ -14696,7 +14699,7 @@
         <v>7</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>118</v>
@@ -14722,10 +14725,10 @@
         <v>119</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>122</v>
@@ -14751,10 +14754,10 @@
         <v>123</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>125</v>
@@ -14780,10 +14783,10 @@
         <v>127</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>129</v>
@@ -14812,7 +14815,7 @@
         <v>24</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>132</v>
@@ -14838,10 +14841,10 @@
         <v>133</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>135</v>
@@ -14870,7 +14873,7 @@
         <v>34</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>137</v>
@@ -14893,16 +14896,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -14922,16 +14925,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -14951,16 +14954,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -14980,7 +14983,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>52</v>
@@ -14989,7 +14992,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -15009,13 +15012,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>
@@ -15091,7 +15094,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -15111,7 +15114,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -15128,10 +15131,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -15151,7 +15154,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -15168,10 +15171,10 @@
         <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -15191,7 +15194,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -15211,7 +15214,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -15231,7 +15234,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -15251,7 +15254,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -15291,7 +15294,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -15308,10 +15311,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -15331,7 +15334,7 @@
         <v>62</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -15348,10 +15351,10 @@
         <v>66</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -15371,7 +15374,7 @@
         <v>34</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>72</v>
@@ -15391,7 +15394,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -15431,7 +15434,7 @@
         <v>48</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>81</v>
@@ -15468,10 +15471,10 @@
         <v>84</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>86</v>
@@ -15488,10 +15491,10 @@
         <v>87</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>90</v>
@@ -15508,10 +15511,10 @@
         <v>91</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>94</v>
@@ -15531,7 +15534,7 @@
         <v>62</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>97</v>
@@ -15548,10 +15551,10 @@
         <v>98</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>101</v>
@@ -15571,7 +15574,7 @@
         <v>34</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>104</v>
@@ -15591,7 +15594,7 @@
         <v>39</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>107</v>
@@ -15611,7 +15614,7 @@
         <v>44</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>110</v>
@@ -15631,7 +15634,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -15671,7 +15674,7 @@
         <v>7</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>118</v>
@@ -15688,10 +15691,10 @@
         <v>119</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>122</v>
@@ -15708,10 +15711,10 @@
         <v>123</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>125</v>
@@ -15731,7 +15734,7 @@
         <v>24</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>129</v>
@@ -15748,10 +15751,10 @@
         <v>130</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>132</v>
@@ -15771,7 +15774,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>135</v>
@@ -15791,7 +15794,7 @@
         <v>39</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>137</v>
@@ -15805,16 +15808,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>7</v>
@@ -15825,16 +15828,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>7</v>
@@ -15845,7 +15848,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>52</v>
@@ -15854,7 +15857,7 @@
         <v>7</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>7</v>
@@ -15865,16 +15868,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -15930,7 +15933,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -15939,13 +15942,13 @@
         <v>7</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -15959,7 +15962,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -15971,10 +15974,10 @@
         <v>7</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -15985,10 +15988,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -16003,7 +16006,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -16014,10 +16017,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -16032,7 +16035,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -16046,7 +16049,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -16061,7 +16064,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -16072,10 +16075,10 @@
         <v>33</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>36</v>
@@ -16090,7 +16093,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -16104,7 +16107,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -16130,7 +16133,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -16159,7 +16162,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -16188,7 +16191,7 @@
         <v>48</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>53</v>
@@ -16211,7 +16214,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>52</v>
@@ -16220,7 +16223,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>7</v>
@@ -16246,7 +16249,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>56</v>
@@ -16272,10 +16275,10 @@
         <v>57</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>60</v>
@@ -16301,10 +16304,10 @@
         <v>61</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>64</v>
@@ -16333,7 +16336,7 @@
         <v>24</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>69</v>
@@ -16359,10 +16362,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>72</v>
@@ -16391,7 +16394,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>75</v>
@@ -16420,7 +16423,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>78</v>
@@ -16449,7 +16452,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>81</v>
@@ -16478,7 +16481,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>83</v>
@@ -16501,7 +16504,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>52</v>
@@ -16510,7 +16513,7 @@
         <v>7</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>7</v>
@@ -16536,7 +16539,7 @@
         <v>7</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>86</v>
@@ -16562,10 +16565,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>90</v>
@@ -16591,10 +16594,10 @@
         <v>91</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>94</v>
@@ -16620,10 +16623,10 @@
         <v>95</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>97</v>
@@ -16652,7 +16655,7 @@
         <v>24</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>101</v>
@@ -16678,10 +16681,10 @@
         <v>102</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>104</v>
@@ -16710,7 +16713,7 @@
         <v>34</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>107</v>
@@ -16739,7 +16742,7 @@
         <v>39</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>110</v>
@@ -16768,7 +16771,7 @@
         <v>44</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>113</v>
@@ -16797,7 +16800,7 @@
         <v>48</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>115</v>
@@ -16820,7 +16823,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>52</v>
@@ -16829,7 +16832,7 @@
         <v>7</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>7</v>
@@ -16855,7 +16858,7 @@
         <v>7</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>118</v>
@@ -16881,10 +16884,10 @@
         <v>119</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>122</v>
@@ -16913,7 +16916,7 @@
         <v>24</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>125</v>
@@ -16939,10 +16942,10 @@
         <v>127</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>129</v>
@@ -16971,7 +16974,7 @@
         <v>34</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>132</v>
@@ -17000,7 +17003,7 @@
         <v>39</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>135</v>
@@ -17029,7 +17032,7 @@
         <v>44</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>137</v>
@@ -17052,16 +17055,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>7</v>
@@ -17081,7 +17084,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>52</v>
@@ -17090,7 +17093,7 @@
         <v>7</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>7</v>
@@ -17110,16 +17113,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>7</v>

--- a/src/main/java/video/call/data/topics.xlsx
+++ b/src/main/java/video/call/data/topics.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="754">
   <si>
     <t>Part</t>
   </si>
@@ -1987,7 +1987,7 @@
     <t>We had so much fun talking about transportation. I'll see you in the next lesson. Bye bye!</t>
   </si>
   <si>
-    <t xml:space="preserve">Hi, Amy's birthday is coming soon. Let's get her some new items of clothes. </t>
+    <t>Hi, Amy's birthday is coming soon. Let's get her some new items of clothes.</t>
   </si>
   <si>
     <t>Jeans, pink dress, red dress, hat</t>
@@ -2045,6 +2045,12 @@
   </si>
   <si>
     <t>So, are they too big or too small for her?</t>
+  </si>
+  <si>
+    <t>1_11</t>
+  </si>
+  <si>
+    <t>1_12</t>
   </si>
   <si>
     <t>How about getting her a dress? Which one is better, purple or white?</t>
@@ -2091,6 +2097,12 @@
   </si>
   <si>
     <t>I think she would like the purple dress.</t>
+  </si>
+  <si>
+    <t>2_12</t>
+  </si>
+  <si>
+    <t>2_13</t>
   </si>
   <si>
     <t>Look at this hat. Do you think it fits her?</t>
@@ -5156,7 +5168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>665</v>
@@ -5185,7 +5197,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>289</v>
@@ -5214,7 +5226,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>292</v>
@@ -5243,7 +5255,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>670</v>
@@ -5269,7 +5281,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>34</v>
@@ -5295,7 +5307,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>39</v>
@@ -5324,7 +5336,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>44</v>
@@ -5353,7 +5365,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>23</v>
+        <v>674</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>48</v>
@@ -5382,7 +5394,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>47</v>
+        <v>675</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>52</v>
@@ -5411,13 +5423,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>526</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>56</v>
@@ -5443,10 +5455,10 @@
         <v>57</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>60</v>
@@ -5472,10 +5484,10 @@
         <v>61</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>64</v>
@@ -5501,10 +5513,10 @@
         <v>66</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>69</v>
@@ -5530,10 +5542,10 @@
         <v>70</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>72</v>
@@ -5556,13 +5568,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>69</v>
@@ -5585,13 +5597,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>292</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>75</v>
@@ -5614,13 +5626,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>78</v>
@@ -5643,13 +5655,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>81</v>
@@ -5672,13 +5684,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>83</v>
@@ -5701,13 +5713,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>44</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>197</v>
@@ -5730,13 +5742,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>82</v>
+        <v>691</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>83</v>
@@ -5759,7 +5771,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>198</v>
+        <v>692</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>52</v>
@@ -5794,7 +5806,7 @@
         <v>7</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>86</v>
@@ -5820,10 +5832,10 @@
         <v>87</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>90</v>
@@ -5849,10 +5861,10 @@
         <v>91</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>94</v>
@@ -5881,7 +5893,7 @@
         <v>62</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>97</v>
@@ -5907,10 +5919,10 @@
         <v>98</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>101</v>
@@ -5939,7 +5951,7 @@
         <v>34</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>104</v>
@@ -5968,7 +5980,7 @@
         <v>39</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>107</v>
@@ -5997,7 +6009,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>110</v>
@@ -6026,7 +6038,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>107</v>
@@ -6084,7 +6096,7 @@
         <v>7</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>160</v>
@@ -6152,7 +6164,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -6164,10 +6176,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>7</v>
@@ -6181,7 +6193,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -6196,7 +6208,7 @@
         <v>7</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>7</v>
@@ -6207,10 +6219,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>20</v>
@@ -6219,13 +6231,13 @@
         <v>21</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>7</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>7</v>
@@ -6239,7 +6251,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>26</v>
@@ -6254,7 +6266,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>7</v>
@@ -6268,7 +6280,7 @@
         <v>512</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>31</v>
@@ -6283,7 +6295,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>7</v>
@@ -6312,7 +6324,7 @@
         <v>7</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>7</v>
@@ -6326,7 +6338,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>41</v>
@@ -6335,7 +6347,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>7</v>
@@ -6355,7 +6367,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>46</v>
@@ -6384,7 +6396,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>50</v>
@@ -6393,7 +6405,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>7</v>
@@ -6442,7 +6454,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>56</v>
@@ -6468,10 +6480,10 @@
         <v>57</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>60</v>
@@ -6500,7 +6512,7 @@
         <v>62</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>64</v>
@@ -6529,7 +6541,7 @@
         <v>29</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>69</v>
@@ -6587,7 +6599,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>75</v>
@@ -6616,7 +6628,7 @@
         <v>44</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>78</v>
@@ -6645,7 +6657,7 @@
         <v>48</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>81</v>
@@ -6703,7 +6715,7 @@
         <v>7</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>86</v>
@@ -6729,10 +6741,10 @@
         <v>87</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>90</v>
@@ -6761,7 +6773,7 @@
         <v>62</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>94</v>
@@ -6787,10 +6799,10 @@
         <v>95</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>97</v>
@@ -6819,7 +6831,7 @@
         <v>34</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>101</v>
@@ -6848,7 +6860,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>104</v>
@@ -6877,7 +6889,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>107</v>
@@ -6906,7 +6918,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>110</v>
@@ -6964,7 +6976,7 @@
         <v>7</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>118</v>
@@ -6973,7 +6985,7 @@
         <v>7</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>7</v>
@@ -6990,10 +7002,10 @@
         <v>119</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>122</v>
@@ -7019,10 +7031,10 @@
         <v>123</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>125</v>
@@ -7051,7 +7063,7 @@
         <v>315</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>129</v>
@@ -7080,7 +7092,7 @@
         <v>24</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>132</v>
@@ -7106,10 +7118,10 @@
         <v>133</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>135</v>
@@ -7138,7 +7150,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>137</v>
@@ -7167,7 +7179,7 @@
         <v>39</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>223</v>
@@ -7196,7 +7208,7 @@
         <v>44</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>226</v>
@@ -7225,7 +7237,7 @@
         <v>48</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>228</v>
@@ -7283,7 +7295,7 @@
         <v>7</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D41" t="s" s="0">
         <v>160</v>
